--- a/Study.xlsx
+++ b/Study.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\DH_Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AAC0F50-C151-4750-94AD-5454E41B7CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DFC29F3-7BDE-4B3E-9DEA-87CAC63C5B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1424,6 +1424,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1490,12 +1493,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1504,9 +1507,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1825,14 +1825,14 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="82" t="s">
         <v>221</v>
       </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81" t="s">
+      <c r="D1" s="82"/>
+      <c r="E1" s="82" t="s">
         <v>225</v>
       </c>
-      <c r="F1" s="81"/>
+      <c r="F1" s="82"/>
       <c r="G1" s="4" t="s">
         <v>222</v>
       </c>
@@ -1841,19 +1841,19 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="69" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="82">
+      <c r="C2" s="83">
         <v>0</v>
       </c>
       <c r="D2" s="6">
         <v>0</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="E2" s="83" t="s">
         <v>224</v>
       </c>
       <c r="F2" s="6" t="s">
@@ -1863,15 +1863,15 @@
       <c r="H2" s="17"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="68"/>
+      <c r="A3" s="69"/>
       <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="82"/>
+      <c r="C3" s="83"/>
       <c r="D3" s="6">
         <v>0</v>
       </c>
-      <c r="E3" s="82"/>
+      <c r="E3" s="83"/>
       <c r="F3" s="6" t="s">
         <v>224</v>
       </c>
@@ -1879,15 +1879,15 @@
       <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="68"/>
+      <c r="A4" s="69"/>
       <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="82"/>
+      <c r="C4" s="83"/>
       <c r="D4" s="6">
         <v>0</v>
       </c>
-      <c r="E4" s="82"/>
+      <c r="E4" s="83"/>
       <c r="F4" s="6" t="s">
         <v>224</v>
       </c>
@@ -1895,15 +1895,15 @@
       <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="68"/>
+      <c r="A5" s="69"/>
       <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="82"/>
+      <c r="C5" s="83"/>
       <c r="D5" s="6">
         <v>0</v>
       </c>
-      <c r="E5" s="82"/>
+      <c r="E5" s="83"/>
       <c r="F5" s="6" t="s">
         <v>224</v>
       </c>
@@ -1911,15 +1911,15 @@
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="68"/>
+      <c r="A6" s="69"/>
       <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="82"/>
+      <c r="C6" s="83"/>
       <c r="D6" s="6">
         <v>0</v>
       </c>
-      <c r="E6" s="82"/>
+      <c r="E6" s="83"/>
       <c r="F6" s="6" t="s">
         <v>224</v>
       </c>
@@ -1927,15 +1927,15 @@
       <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="68"/>
+      <c r="A7" s="69"/>
       <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="82"/>
+      <c r="C7" s="83"/>
       <c r="D7" s="6">
         <v>0</v>
       </c>
-      <c r="E7" s="82"/>
+      <c r="E7" s="83"/>
       <c r="F7" s="6" t="s">
         <v>224</v>
       </c>
@@ -1943,15 +1943,15 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="68"/>
+      <c r="A8" s="69"/>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="82"/>
+      <c r="C8" s="83"/>
       <c r="D8" s="6">
         <v>0</v>
       </c>
-      <c r="E8" s="82"/>
+      <c r="E8" s="83"/>
       <c r="F8" s="6" t="s">
         <v>224</v>
       </c>
@@ -1959,19 +1959,19 @@
       <c r="H8" s="17"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="69" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="82">
+      <c r="C9" s="83">
         <v>0</v>
       </c>
       <c r="D9" s="6">
         <v>0</v>
       </c>
-      <c r="E9" s="82" t="s">
+      <c r="E9" s="83" t="s">
         <v>224</v>
       </c>
       <c r="F9" s="6" t="s">
@@ -1981,15 +1981,15 @@
       <c r="H9" s="15"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="68"/>
+      <c r="A10" s="69"/>
       <c r="B10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="82"/>
+      <c r="C10" s="83"/>
       <c r="D10" s="6">
         <v>0</v>
       </c>
-      <c r="E10" s="82"/>
+      <c r="E10" s="83"/>
       <c r="F10" s="6" t="s">
         <v>224</v>
       </c>
@@ -1997,15 +1997,15 @@
       <c r="H10" s="15"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="68"/>
+      <c r="A11" s="69"/>
       <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="82"/>
+      <c r="C11" s="83"/>
       <c r="D11" s="6">
         <v>0</v>
       </c>
-      <c r="E11" s="82"/>
+      <c r="E11" s="83"/>
       <c r="F11" s="6" t="s">
         <v>224</v>
       </c>
@@ -2013,15 +2013,15 @@
       <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="68"/>
+      <c r="A12" s="69"/>
       <c r="B12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="82"/>
+      <c r="C12" s="83"/>
       <c r="D12" s="6">
         <v>0</v>
       </c>
-      <c r="E12" s="82"/>
+      <c r="E12" s="83"/>
       <c r="F12" s="6" t="s">
         <v>224</v>
       </c>
@@ -2029,15 +2029,15 @@
       <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="68"/>
+      <c r="A13" s="69"/>
       <c r="B13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="82"/>
+      <c r="C13" s="83"/>
       <c r="D13" s="6">
         <v>0</v>
       </c>
-      <c r="E13" s="82"/>
+      <c r="E13" s="83"/>
       <c r="F13" s="6" t="s">
         <v>224</v>
       </c>
@@ -2045,15 +2045,15 @@
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="68"/>
+      <c r="A14" s="69"/>
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="82"/>
+      <c r="C14" s="83"/>
       <c r="D14" s="6">
         <v>0</v>
       </c>
-      <c r="E14" s="82"/>
+      <c r="E14" s="83"/>
       <c r="F14" s="6" t="s">
         <v>224</v>
       </c>
@@ -2061,15 +2061,15 @@
       <c r="H14" s="17"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="68"/>
+      <c r="A15" s="69"/>
       <c r="B15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="82"/>
+      <c r="C15" s="83"/>
       <c r="D15" s="6">
         <v>0</v>
       </c>
-      <c r="E15" s="82"/>
+      <c r="E15" s="83"/>
       <c r="F15" s="6" t="s">
         <v>224</v>
       </c>
@@ -2077,15 +2077,15 @@
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="68"/>
+      <c r="A16" s="69"/>
       <c r="B16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="82"/>
+      <c r="C16" s="83"/>
       <c r="D16" s="6">
         <v>0</v>
       </c>
-      <c r="E16" s="82"/>
+      <c r="E16" s="83"/>
       <c r="F16" s="6" t="s">
         <v>224</v>
       </c>
@@ -2093,19 +2093,19 @@
       <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="69" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="82">
+      <c r="C17" s="83">
         <v>0</v>
       </c>
       <c r="D17" s="6">
         <v>0</v>
       </c>
-      <c r="E17" s="82" t="s">
+      <c r="E17" s="83" t="s">
         <v>224</v>
       </c>
       <c r="F17" s="6" t="s">
@@ -2115,15 +2115,15 @@
       <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="68"/>
+      <c r="A18" s="69"/>
       <c r="B18" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="82"/>
+      <c r="C18" s="83"/>
       <c r="D18" s="6">
         <v>0</v>
       </c>
-      <c r="E18" s="82"/>
+      <c r="E18" s="83"/>
       <c r="F18" s="6" t="s">
         <v>224</v>
       </c>
@@ -2131,27 +2131,27 @@
       <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="68"/>
+      <c r="A19" s="69"/>
       <c r="B19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="82"/>
+      <c r="C19" s="83"/>
       <c r="D19" s="6">
         <v>0</v>
       </c>
-      <c r="E19" s="82"/>
+      <c r="E19" s="83"/>
       <c r="F19" s="58" t="s">
         <v>224</v>
       </c>
       <c r="G19" s="45"/>
-      <c r="H19" s="88"/>
+      <c r="H19" s="61"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="68"/>
+      <c r="A20" s="69"/>
       <c r="B20" t="s">
         <v>254</v>
       </c>
-      <c r="C20" s="82"/>
+      <c r="C20" s="83"/>
       <c r="D20" s="2">
         <v>0</v>
       </c>
@@ -2163,13 +2163,13 @@
       <c r="H20" s="22"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="69" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="82">
+      <c r="C21" s="83">
         <v>0</v>
       </c>
       <c r="D21" s="6">
@@ -2185,11 +2185,11 @@
       <c r="H21" s="22"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="68"/>
+      <c r="A22" s="69"/>
       <c r="B22" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="82"/>
+      <c r="C22" s="83"/>
       <c r="D22" s="6">
         <v>0</v>
       </c>
@@ -2201,15 +2201,15 @@
       <c r="H22" s="22"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="68"/>
+      <c r="A23" s="69"/>
       <c r="B23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="82"/>
+      <c r="C23" s="83"/>
       <c r="D23" s="6">
         <v>0</v>
       </c>
-      <c r="E23" s="82"/>
+      <c r="E23" s="83"/>
       <c r="F23" s="59" t="s">
         <v>224</v>
       </c>
@@ -2217,15 +2217,15 @@
       <c r="H23" s="32"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="68"/>
+      <c r="A24" s="69"/>
       <c r="B24" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="82"/>
+      <c r="C24" s="83"/>
       <c r="D24" s="6">
         <v>0</v>
       </c>
-      <c r="E24" s="82"/>
+      <c r="E24" s="83"/>
       <c r="F24" s="6" t="s">
         <v>226</v>
       </c>
@@ -2233,15 +2233,15 @@
       <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="68"/>
+      <c r="A25" s="69"/>
       <c r="B25" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="82"/>
+      <c r="C25" s="83"/>
       <c r="D25" s="6">
         <v>0</v>
       </c>
-      <c r="E25" s="82"/>
+      <c r="E25" s="83"/>
       <c r="F25" s="6" t="s">
         <v>227</v>
       </c>
@@ -2249,19 +2249,19 @@
       <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="68" t="s">
+      <c r="A26" s="69" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C26" s="82">
+      <c r="C26" s="83">
         <v>0</v>
       </c>
       <c r="D26" s="6">
         <v>0</v>
       </c>
-      <c r="E26" s="82" t="s">
+      <c r="E26" s="83" t="s">
         <v>224</v>
       </c>
       <c r="F26" s="6" t="s">
@@ -2271,15 +2271,15 @@
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="68"/>
+      <c r="A27" s="69"/>
       <c r="B27" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="82"/>
+      <c r="C27" s="83"/>
       <c r="D27" s="6">
         <v>0</v>
       </c>
-      <c r="E27" s="82"/>
+      <c r="E27" s="83"/>
       <c r="F27" s="6" t="s">
         <v>226</v>
       </c>
@@ -2287,15 +2287,15 @@
       <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="68"/>
+      <c r="A28" s="69"/>
       <c r="B28" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="82"/>
+      <c r="C28" s="83"/>
       <c r="D28" s="6">
         <v>0</v>
       </c>
-      <c r="E28" s="82"/>
+      <c r="E28" s="83"/>
       <c r="F28" s="6" t="s">
         <v>226</v>
       </c>
@@ -2303,15 +2303,15 @@
       <c r="H28" s="17"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="68"/>
+      <c r="A29" s="69"/>
       <c r="B29" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="82"/>
+      <c r="C29" s="83"/>
       <c r="D29" s="6">
         <v>0</v>
       </c>
-      <c r="E29" s="82"/>
+      <c r="E29" s="83"/>
       <c r="F29" s="6" t="s">
         <v>226</v>
       </c>
@@ -2319,15 +2319,15 @@
       <c r="H29" s="17"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="68"/>
+      <c r="A30" s="69"/>
       <c r="B30" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="82"/>
+      <c r="C30" s="83"/>
       <c r="D30" s="6">
         <v>0</v>
       </c>
-      <c r="E30" s="82"/>
+      <c r="E30" s="83"/>
       <c r="F30" s="6" t="s">
         <v>224</v>
       </c>
@@ -2335,47 +2335,47 @@
       <c r="H30" s="17"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="68"/>
+      <c r="A31" s="69"/>
       <c r="B31" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="82"/>
+      <c r="C31" s="83"/>
       <c r="D31" s="6">
         <v>0</v>
       </c>
-      <c r="E31" s="82"/>
+      <c r="E31" s="83"/>
       <c r="F31" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="7"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="68"/>
+      <c r="A32" s="69"/>
       <c r="B32" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="82"/>
+      <c r="C32" s="83"/>
       <c r="D32" s="6">
         <v>0</v>
       </c>
-      <c r="E32" s="82"/>
+      <c r="E32" s="83"/>
       <c r="F32" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="7"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="68"/>
+      <c r="A33" s="69"/>
       <c r="B33" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="82"/>
+      <c r="C33" s="83"/>
       <c r="D33" s="6">
         <v>0</v>
       </c>
-      <c r="E33" s="82"/>
+      <c r="E33" s="83"/>
       <c r="F33" s="6" t="s">
         <v>227</v>
       </c>
@@ -2383,19 +2383,19 @@
       <c r="H33" s="7"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="68" t="s">
+      <c r="A34" s="69" t="s">
         <v>38</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="82">
+      <c r="C34" s="83">
         <v>1</v>
       </c>
       <c r="D34" s="6">
         <v>1</v>
       </c>
-      <c r="E34" s="82" t="s">
+      <c r="E34" s="83" t="s">
         <v>224</v>
       </c>
       <c r="F34" s="6" t="s">
@@ -2405,15 +2405,15 @@
       <c r="H34" s="9"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="68"/>
+      <c r="A35" s="69"/>
       <c r="B35" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="82"/>
+      <c r="C35" s="83"/>
       <c r="D35" s="6">
         <v>1</v>
       </c>
-      <c r="E35" s="82"/>
+      <c r="E35" s="83"/>
       <c r="F35" s="6" t="s">
         <v>224</v>
       </c>
@@ -2421,15 +2421,15 @@
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="68"/>
+      <c r="A36" s="69"/>
       <c r="B36" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="82"/>
+      <c r="C36" s="83"/>
       <c r="D36" s="6">
         <v>1</v>
       </c>
-      <c r="E36" s="82"/>
+      <c r="E36" s="83"/>
       <c r="F36" s="6" t="s">
         <v>224</v>
       </c>
@@ -2437,67 +2437,67 @@
       <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="68"/>
+      <c r="A37" s="69"/>
       <c r="B37" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="82"/>
+      <c r="C37" s="83"/>
       <c r="D37" s="25"/>
-      <c r="E37" s="82"/>
+      <c r="E37" s="83"/>
       <c r="F37" s="25"/>
       <c r="G37" s="25"/>
       <c r="H37"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="69"/>
+      <c r="A38" s="70"/>
       <c r="B38" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="C38" s="83"/>
+      <c r="C38" s="85"/>
       <c r="D38" s="25"/>
-      <c r="E38" s="82"/>
+      <c r="E38" s="83"/>
       <c r="F38" s="25"/>
       <c r="G38" s="29"/>
       <c r="H38" s="22"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="69"/>
+      <c r="A39" s="70"/>
       <c r="B39" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="C39" s="83"/>
+      <c r="C39" s="85"/>
       <c r="D39" s="25"/>
-      <c r="E39" s="82"/>
+      <c r="E39" s="83"/>
       <c r="F39" s="25"/>
       <c r="G39" s="29"/>
       <c r="H39" s="22"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="69"/>
+      <c r="A40" s="70"/>
       <c r="B40" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="C40" s="83"/>
+      <c r="C40" s="85"/>
       <c r="D40" s="6"/>
-      <c r="E40" s="82"/>
+      <c r="E40" s="83"/>
       <c r="F40" s="6"/>
       <c r="G40" s="29"/>
       <c r="H40" s="22"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="71" t="s">
+      <c r="A41" s="72" t="s">
         <v>47</v>
       </c>
       <c r="B41" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="C41" s="82">
+      <c r="C41" s="83">
         <v>1</v>
       </c>
       <c r="D41" s="6">
         <v>0</v>
       </c>
-      <c r="E41" s="82" t="s">
+      <c r="E41" s="83" t="s">
         <v>226</v>
       </c>
       <c r="F41" s="6" t="s">
@@ -2507,15 +2507,15 @@
       <c r="H41" s="32"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="71"/>
+      <c r="A42" s="72"/>
       <c r="B42" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="82"/>
+      <c r="C42" s="83"/>
       <c r="D42" s="6">
         <v>1</v>
       </c>
-      <c r="E42" s="82"/>
+      <c r="E42" s="83"/>
       <c r="F42" s="6" t="s">
         <v>226</v>
       </c>
@@ -2523,15 +2523,15 @@
       <c r="H42" s="17"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="71"/>
+      <c r="A43" s="72"/>
       <c r="B43" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="82"/>
+      <c r="C43" s="83"/>
       <c r="D43" s="6">
         <v>1</v>
       </c>
-      <c r="E43" s="82"/>
+      <c r="E43" s="83"/>
       <c r="F43" s="6" t="s">
         <v>226</v>
       </c>
@@ -2539,15 +2539,15 @@
       <c r="H43" s="17"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="71"/>
+      <c r="A44" s="72"/>
       <c r="B44" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="82"/>
+      <c r="C44" s="83"/>
       <c r="D44" s="6">
         <v>1</v>
       </c>
-      <c r="E44" s="82"/>
+      <c r="E44" s="83"/>
       <c r="F44" s="6" t="s">
         <v>226</v>
       </c>
@@ -2555,15 +2555,15 @@
       <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="71"/>
+      <c r="A45" s="72"/>
       <c r="B45" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="82"/>
+      <c r="C45" s="83"/>
       <c r="D45" s="6">
         <v>1</v>
       </c>
-      <c r="E45" s="82"/>
+      <c r="E45" s="83"/>
       <c r="F45" s="6" t="s">
         <v>226</v>
       </c>
@@ -2571,15 +2571,15 @@
       <c r="H45" s="17"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="71"/>
+      <c r="A46" s="72"/>
       <c r="B46" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="C46" s="82"/>
+      <c r="C46" s="83"/>
       <c r="D46" s="6">
         <v>1</v>
       </c>
-      <c r="E46" s="82"/>
+      <c r="E46" s="83"/>
       <c r="F46" s="6" t="s">
         <v>226</v>
       </c>
@@ -2587,15 +2587,15 @@
       <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="71"/>
+      <c r="A47" s="72"/>
       <c r="B47" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C47" s="82"/>
+      <c r="C47" s="83"/>
       <c r="D47" s="6">
         <v>1</v>
       </c>
-      <c r="E47" s="82"/>
+      <c r="E47" s="83"/>
       <c r="F47" s="6" t="s">
         <v>226</v>
       </c>
@@ -2603,19 +2603,19 @@
       <c r="H47" s="17"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="71" t="s">
+      <c r="A48" s="72" t="s">
         <v>48</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="82">
+      <c r="C48" s="83">
         <v>2</v>
       </c>
       <c r="D48" s="6">
         <v>0</v>
       </c>
-      <c r="E48" s="82" t="s">
+      <c r="E48" s="83" t="s">
         <v>226</v>
       </c>
       <c r="F48" s="6" t="s">
@@ -2625,15 +2625,15 @@
       <c r="H48" s="17"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="71"/>
+      <c r="A49" s="72"/>
       <c r="B49" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="82"/>
+      <c r="C49" s="83"/>
       <c r="D49" s="6">
         <v>2</v>
       </c>
-      <c r="E49" s="82"/>
+      <c r="E49" s="83"/>
       <c r="F49" s="6" t="s">
         <v>226</v>
       </c>
@@ -2641,15 +2641,15 @@
       <c r="H49" s="17"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="71"/>
+      <c r="A50" s="72"/>
       <c r="B50" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C50" s="82"/>
+      <c r="C50" s="83"/>
       <c r="D50" s="6">
         <v>2</v>
       </c>
-      <c r="E50" s="82"/>
+      <c r="E50" s="83"/>
       <c r="F50" s="6" t="s">
         <v>226</v>
       </c>
@@ -2657,15 +2657,15 @@
       <c r="H50" s="17"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="71"/>
+      <c r="A51" s="72"/>
       <c r="B51" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C51" s="82"/>
+      <c r="C51" s="83"/>
       <c r="D51" s="6">
         <v>2</v>
       </c>
-      <c r="E51" s="82"/>
+      <c r="E51" s="83"/>
       <c r="F51" s="6" t="s">
         <v>226</v>
       </c>
@@ -2673,15 +2673,15 @@
       <c r="H51" s="17"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="71"/>
+      <c r="A52" s="72"/>
       <c r="B52" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C52" s="82"/>
+      <c r="C52" s="83"/>
       <c r="D52" s="6">
         <v>2</v>
       </c>
-      <c r="E52" s="82"/>
+      <c r="E52" s="83"/>
       <c r="F52" s="6" t="s">
         <v>226</v>
       </c>
@@ -2689,19 +2689,19 @@
       <c r="H52" s="17"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="71" t="s">
+      <c r="A53" s="72" t="s">
         <v>241</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="82">
+      <c r="C53" s="83">
         <v>2</v>
       </c>
       <c r="D53" s="6">
         <v>0</v>
       </c>
-      <c r="E53" s="82" t="s">
+      <c r="E53" s="83" t="s">
         <v>227</v>
       </c>
       <c r="F53" s="6" t="s">
@@ -2711,15 +2711,15 @@
       <c r="H53" s="11"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="71"/>
+      <c r="A54" s="72"/>
       <c r="B54" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C54" s="82"/>
+      <c r="C54" s="83"/>
       <c r="D54" s="6">
         <v>2</v>
       </c>
-      <c r="E54" s="82"/>
+      <c r="E54" s="83"/>
       <c r="F54" s="6" t="s">
         <v>227</v>
       </c>
@@ -2727,15 +2727,15 @@
       <c r="H54" s="11"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="71"/>
+      <c r="A55" s="72"/>
       <c r="B55" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C55" s="82"/>
+      <c r="C55" s="83"/>
       <c r="D55" s="6">
         <v>2</v>
       </c>
-      <c r="E55" s="82"/>
+      <c r="E55" s="83"/>
       <c r="F55" s="6" t="s">
         <v>227</v>
       </c>
@@ -2743,15 +2743,15 @@
       <c r="H55" s="11"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="71"/>
+      <c r="A56" s="72"/>
       <c r="B56" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C56" s="82"/>
+      <c r="C56" s="83"/>
       <c r="D56" s="6">
         <v>2</v>
       </c>
-      <c r="E56" s="82"/>
+      <c r="E56" s="83"/>
       <c r="F56" s="6" t="s">
         <v>227</v>
       </c>
@@ -2759,15 +2759,15 @@
       <c r="H56" s="10"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="71"/>
+      <c r="A57" s="72"/>
       <c r="B57" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="C57" s="82"/>
+      <c r="C57" s="83"/>
       <c r="D57" s="6">
         <v>2</v>
       </c>
-      <c r="E57" s="82"/>
+      <c r="E57" s="83"/>
       <c r="F57" s="6" t="s">
         <v>227</v>
       </c>
@@ -2775,15 +2775,15 @@
       <c r="H57" s="11"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="71"/>
+      <c r="A58" s="72"/>
       <c r="B58" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="C58" s="82"/>
+      <c r="C58" s="83"/>
       <c r="D58" s="6">
         <v>2</v>
       </c>
-      <c r="E58" s="82"/>
+      <c r="E58" s="83"/>
       <c r="F58" s="37" t="s">
         <v>227</v>
       </c>
@@ -2791,11 +2791,11 @@
       <c r="H58" s="43"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="71"/>
+      <c r="A59" s="72"/>
       <c r="B59" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C59" s="82"/>
+      <c r="C59" s="83"/>
       <c r="D59" s="6">
         <v>0</v>
       </c>
@@ -2807,11 +2807,11 @@
       <c r="H59" s="42"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="71"/>
+      <c r="A60" s="72"/>
       <c r="B60" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="C60" s="82"/>
+      <c r="C60" s="83"/>
       <c r="D60" s="38">
         <v>2</v>
       </c>
@@ -2823,19 +2823,19 @@
       <c r="H60" s="42"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="71" t="s">
+      <c r="A61" s="72" t="s">
         <v>55</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C61" s="82">
+      <c r="C61" s="83">
         <v>2</v>
       </c>
       <c r="D61" s="6">
         <v>2</v>
       </c>
-      <c r="E61" s="82" t="s">
+      <c r="E61" s="83" t="s">
         <v>227</v>
       </c>
       <c r="F61" s="6" t="s">
@@ -2845,15 +2845,15 @@
       <c r="H61" s="32"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="71"/>
+      <c r="A62" s="72"/>
       <c r="B62" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="82"/>
+      <c r="C62" s="83"/>
       <c r="D62" s="6">
         <v>2</v>
       </c>
-      <c r="E62" s="82"/>
+      <c r="E62" s="83"/>
       <c r="F62" s="6" t="s">
         <v>227</v>
       </c>
@@ -2861,15 +2861,15 @@
       <c r="H62" s="17"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="71"/>
+      <c r="A63" s="72"/>
       <c r="B63" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C63" s="82"/>
+      <c r="C63" s="83"/>
       <c r="D63" s="6">
         <v>2</v>
       </c>
-      <c r="E63" s="82"/>
+      <c r="E63" s="83"/>
       <c r="F63" s="6" t="s">
         <v>227</v>
       </c>
@@ -2877,15 +2877,15 @@
       <c r="H63" s="17"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="71"/>
+      <c r="A64" s="72"/>
       <c r="B64" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C64" s="82"/>
+      <c r="C64" s="83"/>
       <c r="D64" s="6">
         <v>2</v>
       </c>
-      <c r="E64" s="82"/>
+      <c r="E64" s="83"/>
       <c r="F64" s="6" t="s">
         <v>227</v>
       </c>
@@ -2893,15 +2893,15 @@
       <c r="H64" s="17"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="71"/>
+      <c r="A65" s="72"/>
       <c r="B65" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C65" s="82"/>
+      <c r="C65" s="83"/>
       <c r="D65" s="6">
         <v>2</v>
       </c>
-      <c r="E65" s="82"/>
+      <c r="E65" s="83"/>
       <c r="F65" s="6" t="s">
         <v>227</v>
       </c>
@@ -2909,15 +2909,15 @@
       <c r="H65" s="30"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="71"/>
+      <c r="A66" s="72"/>
       <c r="B66" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C66" s="82"/>
+      <c r="C66" s="83"/>
       <c r="D66" s="6">
         <v>2</v>
       </c>
-      <c r="E66" s="82"/>
+      <c r="E66" s="83"/>
       <c r="F66" s="6" t="s">
         <v>227</v>
       </c>
@@ -2925,19 +2925,19 @@
       <c r="H66" s="30"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="72" t="s">
+      <c r="A67" s="73" t="s">
         <v>61</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C67" s="82">
+      <c r="C67" s="83">
         <v>2</v>
       </c>
       <c r="D67" s="6">
         <v>2</v>
       </c>
-      <c r="E67" s="82" t="s">
+      <c r="E67" s="83" t="s">
         <v>226</v>
       </c>
       <c r="F67" s="6" t="s">
@@ -2947,15 +2947,15 @@
       <c r="H67" s="17"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="72"/>
+      <c r="A68" s="73"/>
       <c r="B68" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C68" s="82"/>
+      <c r="C68" s="83"/>
       <c r="D68" s="6">
         <v>2</v>
       </c>
-      <c r="E68" s="82"/>
+      <c r="E68" s="83"/>
       <c r="F68" s="6" t="s">
         <v>226</v>
       </c>
@@ -2963,19 +2963,19 @@
       <c r="H68" s="17"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="73" t="s">
+      <c r="A69" s="74" t="s">
         <v>239</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="85">
+      <c r="C69" s="86">
         <v>2</v>
       </c>
       <c r="D69" s="6">
         <v>0</v>
       </c>
-      <c r="E69" s="85" t="s">
+      <c r="E69" s="86" t="s">
         <v>226</v>
       </c>
       <c r="F69" s="6" t="s">
@@ -2985,15 +2985,15 @@
       <c r="H69" s="15"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="73"/>
+      <c r="A70" s="74"/>
       <c r="B70" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C70" s="86"/>
+      <c r="C70" s="87"/>
       <c r="D70" s="6">
         <v>0</v>
       </c>
-      <c r="E70" s="86"/>
+      <c r="E70" s="87"/>
       <c r="F70" s="6" t="s">
         <v>227</v>
       </c>
@@ -3001,723 +3001,723 @@
       <c r="H70"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="73"/>
+      <c r="A71" s="74"/>
       <c r="B71" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="86"/>
+      <c r="C71" s="87"/>
       <c r="D71" s="6"/>
-      <c r="E71" s="86"/>
+      <c r="E71" s="87"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="7"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="73"/>
+      <c r="A72" s="74"/>
       <c r="B72" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C72" s="86"/>
+      <c r="C72" s="87"/>
       <c r="D72" s="6"/>
-      <c r="E72" s="86"/>
+      <c r="E72" s="87"/>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
       <c r="H72" s="7"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="73"/>
+      <c r="A73" s="74"/>
       <c r="B73" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C73" s="86"/>
+      <c r="C73" s="87"/>
       <c r="D73" s="6"/>
-      <c r="E73" s="86"/>
+      <c r="E73" s="87"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="7"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="73"/>
+      <c r="A74" s="74"/>
       <c r="B74" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C74" s="86"/>
+      <c r="C74" s="87"/>
       <c r="D74" s="6"/>
-      <c r="E74" s="86"/>
+      <c r="E74" s="87"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
       <c r="H74" s="7"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="73"/>
+      <c r="A75" s="74"/>
       <c r="B75" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="86"/>
+      <c r="C75" s="87"/>
       <c r="D75" s="6"/>
-      <c r="E75" s="86"/>
+      <c r="E75" s="87"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
       <c r="H75" s="7"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="73"/>
+      <c r="A76" s="74"/>
       <c r="B76" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C76" s="86"/>
+      <c r="C76" s="87"/>
       <c r="D76" s="6"/>
-      <c r="E76" s="86"/>
+      <c r="E76" s="87"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="7"/>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="73"/>
+      <c r="A77" s="74"/>
       <c r="B77" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C77" s="86"/>
+      <c r="C77" s="87"/>
       <c r="D77" s="6"/>
-      <c r="E77" s="86"/>
+      <c r="E77" s="87"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
       <c r="H77" s="7"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="73"/>
+      <c r="A78" s="74"/>
       <c r="B78" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C78" s="86"/>
+      <c r="C78" s="87"/>
       <c r="D78" s="6"/>
-      <c r="E78" s="86"/>
+      <c r="E78" s="87"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
       <c r="H78" s="7"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="73"/>
+      <c r="A79" s="74"/>
       <c r="B79" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C79" s="86"/>
+      <c r="C79" s="87"/>
       <c r="D79" s="6"/>
-      <c r="E79" s="86"/>
+      <c r="E79" s="87"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="7"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="73"/>
+      <c r="A80" s="74"/>
       <c r="B80" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C80" s="87"/>
+      <c r="C80" s="88"/>
       <c r="D80" s="6"/>
-      <c r="E80" s="87"/>
+      <c r="E80" s="88"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="7"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="73" t="s">
+      <c r="A81" s="74" t="s">
         <v>76</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C81" s="85"/>
+      <c r="C81" s="86"/>
       <c r="D81" s="6"/>
-      <c r="E81" s="85"/>
+      <c r="E81" s="86"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="7"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="73"/>
+      <c r="A82" s="74"/>
       <c r="B82" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C82" s="86"/>
+      <c r="C82" s="87"/>
       <c r="D82" s="6"/>
-      <c r="E82" s="86"/>
+      <c r="E82" s="87"/>
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
       <c r="H82" s="7"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="73"/>
+      <c r="A83" s="74"/>
       <c r="B83" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C83" s="86"/>
+      <c r="C83" s="87"/>
       <c r="D83" s="6"/>
-      <c r="E83" s="86"/>
+      <c r="E83" s="87"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
       <c r="H83" s="7"/>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="73"/>
+      <c r="A84" s="74"/>
       <c r="B84" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C84" s="86"/>
+      <c r="C84" s="87"/>
       <c r="D84" s="6"/>
-      <c r="E84" s="86"/>
+      <c r="E84" s="87"/>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
       <c r="H84" s="7"/>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="73"/>
+      <c r="A85" s="74"/>
       <c r="B85" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C85" s="86"/>
+      <c r="C85" s="87"/>
       <c r="D85" s="6"/>
-      <c r="E85" s="86"/>
+      <c r="E85" s="87"/>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
       <c r="H85" s="7"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="73"/>
+      <c r="A86" s="74"/>
       <c r="B86" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C86" s="86"/>
+      <c r="C86" s="87"/>
       <c r="D86" s="6"/>
-      <c r="E86" s="86"/>
+      <c r="E86" s="87"/>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
       <c r="H86" s="7"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="73"/>
+      <c r="A87" s="74"/>
       <c r="B87" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C87" s="86"/>
+      <c r="C87" s="87"/>
       <c r="D87" s="6"/>
-      <c r="E87" s="86"/>
+      <c r="E87" s="87"/>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="7"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="73"/>
+      <c r="A88" s="74"/>
       <c r="B88" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C88" s="86"/>
+      <c r="C88" s="87"/>
       <c r="D88" s="6"/>
-      <c r="E88" s="86"/>
+      <c r="E88" s="87"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="7"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="73"/>
+      <c r="A89" s="74"/>
       <c r="B89" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C89" s="87"/>
+      <c r="C89" s="88"/>
       <c r="D89" s="6"/>
-      <c r="E89" s="87"/>
+      <c r="E89" s="88"/>
       <c r="F89" s="6"/>
       <c r="G89" s="12"/>
       <c r="H89" s="13"/>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="73" t="s">
+      <c r="A90" s="74" t="s">
         <v>86</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C90" s="85"/>
+      <c r="C90" s="86"/>
       <c r="D90" s="6"/>
-      <c r="E90" s="85"/>
+      <c r="E90" s="86"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
       <c r="H90" s="7"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="73"/>
+      <c r="A91" s="74"/>
       <c r="B91" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C91" s="86"/>
+      <c r="C91" s="87"/>
       <c r="D91" s="6"/>
-      <c r="E91" s="86"/>
+      <c r="E91" s="87"/>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
       <c r="H91" s="7"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="73"/>
+      <c r="A92" s="74"/>
       <c r="B92" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C92" s="86"/>
+      <c r="C92" s="87"/>
       <c r="D92" s="6"/>
-      <c r="E92" s="86"/>
+      <c r="E92" s="87"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
       <c r="H92" s="7"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="73"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C93" s="86"/>
+      <c r="C93" s="87"/>
       <c r="D93" s="6"/>
-      <c r="E93" s="86"/>
+      <c r="E93" s="87"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
       <c r="H93" s="7"/>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="73"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C94" s="86"/>
+      <c r="C94" s="87"/>
       <c r="D94" s="6"/>
-      <c r="E94" s="86"/>
+      <c r="E94" s="87"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="7"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="73"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C95" s="86"/>
+      <c r="C95" s="87"/>
       <c r="D95" s="6"/>
-      <c r="E95" s="86"/>
+      <c r="E95" s="87"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
       <c r="H95" s="7"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="73"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C96" s="86"/>
+      <c r="C96" s="87"/>
       <c r="D96" s="6"/>
-      <c r="E96" s="86"/>
+      <c r="E96" s="87"/>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="7"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="73"/>
+      <c r="A97" s="74"/>
       <c r="B97" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C97" s="86"/>
+      <c r="C97" s="87"/>
       <c r="D97" s="6"/>
-      <c r="E97" s="86"/>
+      <c r="E97" s="87"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="7"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="73"/>
+      <c r="A98" s="74"/>
       <c r="B98" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C98" s="87"/>
+      <c r="C98" s="88"/>
       <c r="D98" s="6"/>
-      <c r="E98" s="87"/>
+      <c r="E98" s="88"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="7"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="73" t="s">
+      <c r="A99" s="74" t="s">
         <v>96</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C99" s="85"/>
+      <c r="C99" s="86"/>
       <c r="D99" s="6"/>
-      <c r="E99" s="85"/>
+      <c r="E99" s="86"/>
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="7"/>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="73"/>
+      <c r="A100" s="74"/>
       <c r="B100" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C100" s="86"/>
+      <c r="C100" s="87"/>
       <c r="D100" s="6"/>
-      <c r="E100" s="86"/>
+      <c r="E100" s="87"/>
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
       <c r="H100" s="7"/>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="73"/>
+      <c r="A101" s="74"/>
       <c r="B101" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C101" s="86"/>
+      <c r="C101" s="87"/>
       <c r="D101" s="6"/>
-      <c r="E101" s="86"/>
+      <c r="E101" s="87"/>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="7"/>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="73"/>
+      <c r="A102" s="74"/>
       <c r="B102" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C102" s="86"/>
+      <c r="C102" s="87"/>
       <c r="D102" s="6"/>
-      <c r="E102" s="86"/>
+      <c r="E102" s="87"/>
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
       <c r="H102" s="7"/>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="73"/>
+      <c r="A103" s="74"/>
       <c r="B103" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C103" s="87"/>
+      <c r="C103" s="88"/>
       <c r="D103" s="6"/>
-      <c r="E103" s="87"/>
+      <c r="E103" s="88"/>
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
       <c r="H103" s="7"/>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="73" t="s">
+      <c r="A104" s="74" t="s">
         <v>102</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="85"/>
+      <c r="C104" s="86"/>
       <c r="D104" s="6"/>
-      <c r="E104" s="85"/>
+      <c r="E104" s="86"/>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
       <c r="H104" s="7"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="73"/>
+      <c r="A105" s="74"/>
       <c r="B105" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="86"/>
+      <c r="C105" s="87"/>
       <c r="D105" s="6"/>
-      <c r="E105" s="86"/>
+      <c r="E105" s="87"/>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
       <c r="H105" s="7"/>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="73"/>
+      <c r="A106" s="74"/>
       <c r="B106" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="86"/>
+      <c r="C106" s="87"/>
       <c r="D106" s="6"/>
-      <c r="E106" s="86"/>
+      <c r="E106" s="87"/>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="7"/>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="73"/>
+      <c r="A107" s="74"/>
       <c r="B107" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C107" s="86"/>
+      <c r="C107" s="87"/>
       <c r="D107" s="6"/>
-      <c r="E107" s="86"/>
+      <c r="E107" s="87"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
       <c r="H107" s="7"/>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="73"/>
+      <c r="A108" s="74"/>
       <c r="B108" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="86"/>
+      <c r="C108" s="87"/>
       <c r="D108" s="6"/>
-      <c r="E108" s="86"/>
+      <c r="E108" s="87"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
       <c r="H108" s="7"/>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="73"/>
+      <c r="A109" s="74"/>
       <c r="B109" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="87"/>
+      <c r="C109" s="88"/>
       <c r="D109" s="6"/>
-      <c r="E109" s="87"/>
+      <c r="E109" s="88"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
       <c r="H109" s="7"/>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="73" t="s">
+      <c r="A110" s="74" t="s">
         <v>109</v>
       </c>
       <c r="B110" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C110" s="85"/>
+      <c r="C110" s="86"/>
       <c r="D110" s="6"/>
-      <c r="E110" s="85"/>
+      <c r="E110" s="86"/>
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
       <c r="H110" s="7"/>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="73"/>
+      <c r="A111" s="74"/>
       <c r="B111" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C111" s="86"/>
+      <c r="C111" s="87"/>
       <c r="D111" s="6"/>
-      <c r="E111" s="86"/>
+      <c r="E111" s="87"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="7"/>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="73"/>
+      <c r="A112" s="74"/>
       <c r="B112" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C112" s="86"/>
+      <c r="C112" s="87"/>
       <c r="D112" s="6"/>
-      <c r="E112" s="86"/>
+      <c r="E112" s="87"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
       <c r="H112" s="7"/>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="73"/>
+      <c r="A113" s="74"/>
       <c r="B113" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C113" s="86"/>
+      <c r="C113" s="87"/>
       <c r="D113" s="6"/>
-      <c r="E113" s="86"/>
+      <c r="E113" s="87"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
       <c r="H113" s="7"/>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="73"/>
+      <c r="A114" s="74"/>
       <c r="B114" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C114" s="87"/>
+      <c r="C114" s="88"/>
       <c r="D114" s="6"/>
-      <c r="E114" s="87"/>
+      <c r="E114" s="88"/>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="7"/>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="70" t="s">
+      <c r="A115" s="71" t="s">
         <v>115</v>
       </c>
       <c r="B115" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C115" s="85"/>
+      <c r="C115" s="86"/>
       <c r="D115" s="6"/>
-      <c r="E115" s="85"/>
+      <c r="E115" s="86"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="7"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="70"/>
+      <c r="A116" s="71"/>
       <c r="B116" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C116" s="86"/>
+      <c r="C116" s="87"/>
       <c r="D116" s="6"/>
-      <c r="E116" s="86"/>
+      <c r="E116" s="87"/>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
       <c r="H116" s="7"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="70"/>
+      <c r="A117" s="71"/>
       <c r="B117" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C117" s="86"/>
+      <c r="C117" s="87"/>
       <c r="D117" s="6"/>
-      <c r="E117" s="86"/>
+      <c r="E117" s="87"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="7"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="70"/>
+      <c r="A118" s="71"/>
       <c r="B118" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="86"/>
+      <c r="C118" s="87"/>
       <c r="D118" s="6"/>
-      <c r="E118" s="86"/>
+      <c r="E118" s="87"/>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="7"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="70"/>
+      <c r="A119" s="71"/>
       <c r="B119" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="86"/>
+      <c r="C119" s="87"/>
       <c r="D119" s="6"/>
-      <c r="E119" s="86"/>
+      <c r="E119" s="87"/>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
       <c r="H119" s="7"/>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="70"/>
+      <c r="A120" s="71"/>
       <c r="B120" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="86"/>
+      <c r="C120" s="87"/>
       <c r="D120" s="6"/>
-      <c r="E120" s="86"/>
+      <c r="E120" s="87"/>
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
       <c r="H120" s="7"/>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="70"/>
+      <c r="A121" s="71"/>
       <c r="B121" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="87"/>
+      <c r="C121" s="88"/>
       <c r="D121" s="6"/>
-      <c r="E121" s="87"/>
+      <c r="E121" s="88"/>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="7"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="70" t="s">
+      <c r="A122" s="71" t="s">
         <v>121</v>
       </c>
       <c r="B122" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C122" s="85"/>
+      <c r="C122" s="86"/>
       <c r="D122" s="6"/>
-      <c r="E122" s="85"/>
+      <c r="E122" s="86"/>
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
       <c r="H122" s="7"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="70"/>
+      <c r="A123" s="71"/>
       <c r="B123" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C123" s="86"/>
+      <c r="C123" s="87"/>
       <c r="D123" s="6"/>
-      <c r="E123" s="86"/>
+      <c r="E123" s="87"/>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
       <c r="H123" s="7"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="70"/>
+      <c r="A124" s="71"/>
       <c r="B124" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C124" s="86"/>
+      <c r="C124" s="87"/>
       <c r="D124" s="6"/>
-      <c r="E124" s="86"/>
+      <c r="E124" s="87"/>
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
       <c r="H124" s="7"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="70"/>
+      <c r="A125" s="71"/>
       <c r="B125" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C125" s="86"/>
+      <c r="C125" s="87"/>
       <c r="D125" s="6"/>
-      <c r="E125" s="86"/>
+      <c r="E125" s="87"/>
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
       <c r="H125" s="7"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="70"/>
+      <c r="A126" s="71"/>
       <c r="B126" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C126" s="86"/>
+      <c r="C126" s="87"/>
       <c r="D126" s="6"/>
-      <c r="E126" s="86"/>
+      <c r="E126" s="87"/>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
       <c r="H126" s="7"/>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="70"/>
+      <c r="A127" s="71"/>
       <c r="B127" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C127" s="86"/>
+      <c r="C127" s="87"/>
       <c r="D127" s="6"/>
-      <c r="E127" s="86"/>
+      <c r="E127" s="87"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
       <c r="H127" s="7"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="70"/>
+      <c r="A128" s="71"/>
       <c r="B128" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C128" s="86"/>
+      <c r="C128" s="87"/>
       <c r="D128" s="6"/>
-      <c r="E128" s="86"/>
+      <c r="E128" s="87"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
       <c r="H128" s="7"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="70"/>
+      <c r="A129" s="71"/>
       <c r="B129" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C129" s="87"/>
+      <c r="C129" s="88"/>
       <c r="D129" s="6"/>
-      <c r="E129" s="87"/>
+      <c r="E129" s="88"/>
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
       <c r="H129" s="7"/>
@@ -3751,19 +3751,19 @@
       <c r="H131" s="7"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="76" t="s">
+      <c r="A132" s="77" t="s">
         <v>134</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C132" s="85">
+      <c r="C132" s="86">
         <v>3</v>
       </c>
       <c r="D132" s="6">
         <v>0</v>
       </c>
-      <c r="E132" s="85" t="s">
+      <c r="E132" s="86" t="s">
         <v>227</v>
       </c>
       <c r="F132" s="6" t="s">
@@ -3773,15 +3773,15 @@
       <c r="H132" s="17"/>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="76"/>
+      <c r="A133" s="77"/>
       <c r="B133" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="C133" s="86"/>
+      <c r="C133" s="87"/>
       <c r="D133" s="6">
         <v>0</v>
       </c>
-      <c r="E133" s="86"/>
+      <c r="E133" s="87"/>
       <c r="F133" s="6" t="s">
         <v>226</v>
       </c>
@@ -3789,15 +3789,15 @@
       <c r="H133" s="17"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="76"/>
+      <c r="A134" s="77"/>
       <c r="B134" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C134" s="86"/>
+      <c r="C134" s="87"/>
       <c r="D134" s="6">
         <v>1</v>
       </c>
-      <c r="E134" s="86"/>
+      <c r="E134" s="87"/>
       <c r="F134" s="6" t="s">
         <v>227</v>
       </c>
@@ -3805,15 +3805,15 @@
       <c r="H134" s="17"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="76"/>
+      <c r="A135" s="77"/>
       <c r="B135" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C135" s="86"/>
+      <c r="C135" s="87"/>
       <c r="D135" s="6">
         <v>1</v>
       </c>
-      <c r="E135" s="86"/>
+      <c r="E135" s="87"/>
       <c r="F135" s="6" t="s">
         <v>227</v>
       </c>
@@ -3821,15 +3821,15 @@
       <c r="H135" s="17"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="76"/>
+      <c r="A136" s="77"/>
       <c r="B136" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C136" s="86"/>
+      <c r="C136" s="87"/>
       <c r="D136" s="6">
         <v>1</v>
       </c>
-      <c r="E136" s="86"/>
+      <c r="E136" s="87"/>
       <c r="F136" s="6" t="s">
         <v>227</v>
       </c>
@@ -3837,15 +3837,15 @@
       <c r="H136" s="30"/>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="76"/>
+      <c r="A137" s="77"/>
       <c r="B137" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C137" s="86"/>
+      <c r="C137" s="87"/>
       <c r="D137" s="6">
         <v>1</v>
       </c>
-      <c r="E137" s="86"/>
+      <c r="E137" s="87"/>
       <c r="F137" s="6" t="s">
         <v>227</v>
       </c>
@@ -3853,15 +3853,15 @@
       <c r="H137" s="17"/>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="76"/>
+      <c r="A138" s="77"/>
       <c r="B138" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C138" s="86"/>
+      <c r="C138" s="87"/>
       <c r="D138" s="6">
         <v>3</v>
       </c>
-      <c r="E138" s="86"/>
+      <c r="E138" s="87"/>
       <c r="F138" s="6" t="s">
         <v>227</v>
       </c>
@@ -3869,15 +3869,15 @@
       <c r="H138" s="17"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="76"/>
+      <c r="A139" s="77"/>
       <c r="B139" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C139" s="87"/>
+      <c r="C139" s="88"/>
       <c r="D139" s="6">
         <v>3</v>
       </c>
-      <c r="E139" s="87"/>
+      <c r="E139" s="88"/>
       <c r="F139" s="6" t="s">
         <v>227</v>
       </c>
@@ -3885,81 +3885,81 @@
       <c r="H139" s="17"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="77" t="s">
+      <c r="A140" s="78" t="s">
         <v>142</v>
       </c>
       <c r="B140" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C140" s="85"/>
+      <c r="C140" s="86"/>
       <c r="D140" s="6"/>
-      <c r="E140" s="85"/>
+      <c r="E140" s="86"/>
       <c r="F140" s="6"/>
       <c r="G140" s="6"/>
       <c r="H140" s="7"/>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="77"/>
+      <c r="A141" s="78"/>
       <c r="B141" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C141" s="86"/>
+      <c r="C141" s="87"/>
       <c r="D141" s="6"/>
-      <c r="E141" s="86"/>
+      <c r="E141" s="87"/>
       <c r="F141" s="6"/>
       <c r="G141" s="6"/>
       <c r="H141" s="7"/>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="77"/>
+      <c r="A142" s="78"/>
       <c r="B142" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C142" s="86"/>
+      <c r="C142" s="87"/>
       <c r="D142" s="6"/>
-      <c r="E142" s="86"/>
+      <c r="E142" s="87"/>
       <c r="F142" s="6"/>
       <c r="G142" s="6"/>
       <c r="H142" s="7"/>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="77"/>
+      <c r="A143" s="78"/>
       <c r="B143" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C143" s="86"/>
+      <c r="C143" s="87"/>
       <c r="D143" s="6"/>
-      <c r="E143" s="86"/>
+      <c r="E143" s="87"/>
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
       <c r="H143" s="7"/>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="77"/>
+      <c r="A144" s="78"/>
       <c r="B144" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C144" s="87"/>
+      <c r="C144" s="88"/>
       <c r="D144" s="6"/>
-      <c r="E144" s="87"/>
+      <c r="E144" s="88"/>
       <c r="F144" s="6"/>
       <c r="G144" s="6"/>
       <c r="H144" s="7"/>
     </row>
     <row r="145" spans="1:8">
-      <c r="A145" s="77" t="s">
+      <c r="A145" s="78" t="s">
         <v>148</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C145" s="85">
+      <c r="C145" s="86">
         <v>2</v>
       </c>
       <c r="D145" s="6">
         <v>0</v>
       </c>
-      <c r="E145" s="85" t="s">
+      <c r="E145" s="86" t="s">
         <v>227</v>
       </c>
       <c r="F145" s="6" t="s">
@@ -3969,15 +3969,15 @@
       <c r="H145" s="17"/>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" s="77"/>
+      <c r="A146" s="78"/>
       <c r="B146" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C146" s="86"/>
+      <c r="C146" s="87"/>
       <c r="D146" s="6">
         <v>2</v>
       </c>
-      <c r="E146" s="86"/>
+      <c r="E146" s="87"/>
       <c r="F146" s="6" t="s">
         <v>227</v>
       </c>
@@ -3985,15 +3985,15 @@
       <c r="H146" s="7"/>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" s="77"/>
+      <c r="A147" s="78"/>
       <c r="B147" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C147" s="86"/>
+      <c r="C147" s="87"/>
       <c r="D147" s="6">
         <v>2</v>
       </c>
-      <c r="E147" s="86"/>
+      <c r="E147" s="87"/>
       <c r="F147" s="6" t="s">
         <v>227</v>
       </c>
@@ -4001,15 +4001,15 @@
       <c r="H147" s="7"/>
     </row>
     <row r="148" spans="1:8">
-      <c r="A148" s="77"/>
+      <c r="A148" s="78"/>
       <c r="B148" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="C148" s="86"/>
+      <c r="C148" s="87"/>
       <c r="D148" s="6">
         <v>2</v>
       </c>
-      <c r="E148" s="86"/>
+      <c r="E148" s="87"/>
       <c r="F148" s="6" t="s">
         <v>227</v>
       </c>
@@ -4017,15 +4017,15 @@
       <c r="H148" s="7"/>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="77"/>
+      <c r="A149" s="78"/>
       <c r="B149" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C149" s="86"/>
+      <c r="C149" s="87"/>
       <c r="D149" s="6">
         <v>2</v>
       </c>
-      <c r="E149" s="86"/>
+      <c r="E149" s="87"/>
       <c r="F149" s="6" t="s">
         <v>227</v>
       </c>
@@ -4033,15 +4033,15 @@
       <c r="H149" s="7"/>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="77"/>
+      <c r="A150" s="78"/>
       <c r="B150" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C150" s="86"/>
+      <c r="C150" s="87"/>
       <c r="D150" s="6">
         <v>2</v>
       </c>
-      <c r="E150" s="86"/>
+      <c r="E150" s="87"/>
       <c r="F150" s="6" t="s">
         <v>227</v>
       </c>
@@ -4049,15 +4049,15 @@
       <c r="H150" s="7"/>
     </row>
     <row r="151" spans="1:8">
-      <c r="A151" s="77"/>
+      <c r="A151" s="78"/>
       <c r="B151" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C151" s="87"/>
+      <c r="C151" s="88"/>
       <c r="D151" s="6">
         <v>2</v>
       </c>
-      <c r="E151" s="87"/>
+      <c r="E151" s="88"/>
       <c r="F151" s="6" t="s">
         <v>227</v>
       </c>
@@ -4065,143 +4065,143 @@
       <c r="H151" s="7"/>
     </row>
     <row r="152" spans="1:8" ht="18" customHeight="1">
-      <c r="A152" s="78" t="s">
+      <c r="A152" s="79" t="s">
         <v>155</v>
       </c>
       <c r="B152" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C152" s="85"/>
+      <c r="C152" s="86"/>
       <c r="D152" s="6"/>
-      <c r="E152" s="85"/>
+      <c r="E152" s="86"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
       <c r="H152" s="7"/>
     </row>
     <row r="153" spans="1:8">
-      <c r="A153" s="78"/>
+      <c r="A153" s="79"/>
       <c r="B153" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C153" s="86"/>
+      <c r="C153" s="87"/>
       <c r="D153" s="6"/>
-      <c r="E153" s="86"/>
+      <c r="E153" s="87"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
       <c r="H153" s="7"/>
     </row>
     <row r="154" spans="1:8">
-      <c r="A154" s="78"/>
+      <c r="A154" s="79"/>
       <c r="B154" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C154" s="86"/>
+      <c r="C154" s="87"/>
       <c r="D154" s="6"/>
-      <c r="E154" s="86"/>
+      <c r="E154" s="87"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
       <c r="H154" s="7"/>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" s="78"/>
+      <c r="A155" s="79"/>
       <c r="B155" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C155" s="86"/>
+      <c r="C155" s="87"/>
       <c r="D155" s="6"/>
-      <c r="E155" s="86"/>
+      <c r="E155" s="87"/>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
       <c r="H155" s="7"/>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" s="78"/>
+      <c r="A156" s="79"/>
       <c r="B156" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C156" s="86"/>
+      <c r="C156" s="87"/>
       <c r="D156" s="6"/>
-      <c r="E156" s="86"/>
+      <c r="E156" s="87"/>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
       <c r="H156" s="7"/>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" s="78"/>
+      <c r="A157" s="79"/>
       <c r="B157" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C157" s="87"/>
+      <c r="C157" s="88"/>
       <c r="D157" s="6"/>
-      <c r="E157" s="87"/>
+      <c r="E157" s="88"/>
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
       <c r="H157" s="7"/>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="78" t="s">
+      <c r="A158" s="79" t="s">
         <v>162</v>
       </c>
       <c r="B158" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C158" s="85"/>
+      <c r="C158" s="86"/>
       <c r="D158" s="6"/>
-      <c r="E158" s="85"/>
+      <c r="E158" s="86"/>
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
       <c r="H158" s="7"/>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" s="78"/>
+      <c r="A159" s="79"/>
       <c r="B159" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C159" s="86"/>
+      <c r="C159" s="87"/>
       <c r="D159" s="6"/>
-      <c r="E159" s="86"/>
+      <c r="E159" s="87"/>
       <c r="F159" s="6"/>
       <c r="G159" s="6"/>
       <c r="H159" s="7"/>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="78"/>
+      <c r="A160" s="79"/>
       <c r="B160" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C160" s="86"/>
+      <c r="C160" s="87"/>
       <c r="D160" s="6"/>
-      <c r="E160" s="86"/>
+      <c r="E160" s="87"/>
       <c r="F160" s="6"/>
       <c r="G160" s="6"/>
       <c r="H160" s="7"/>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="78"/>
+      <c r="A161" s="79"/>
       <c r="B161" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C161" s="87"/>
+      <c r="C161" s="88"/>
       <c r="D161" s="6"/>
-      <c r="E161" s="87"/>
+      <c r="E161" s="88"/>
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
       <c r="H161" s="7"/>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="79" t="s">
+      <c r="A162" s="80" t="s">
         <v>167</v>
       </c>
       <c r="B162" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C162" s="85">
+      <c r="C162" s="86">
         <v>1</v>
       </c>
       <c r="D162" s="6">
         <v>1</v>
       </c>
-      <c r="E162" s="85" t="s">
+      <c r="E162" s="86" t="s">
         <v>226</v>
       </c>
       <c r="F162" s="6" t="s">
@@ -4211,15 +4211,15 @@
       <c r="H162" s="17"/>
     </row>
     <row r="163" spans="1:8">
-      <c r="A163" s="79"/>
+      <c r="A163" s="80"/>
       <c r="B163" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C163" s="86"/>
+      <c r="C163" s="87"/>
       <c r="D163" s="6">
         <v>0</v>
       </c>
-      <c r="E163" s="86"/>
+      <c r="E163" s="87"/>
       <c r="F163" s="6" t="s">
         <v>224</v>
       </c>
@@ -4227,15 +4227,15 @@
       <c r="H163" s="17"/>
     </row>
     <row r="164" spans="1:8">
-      <c r="A164" s="79"/>
+      <c r="A164" s="80"/>
       <c r="B164" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C164" s="86"/>
+      <c r="C164" s="87"/>
       <c r="D164" s="6">
         <v>1</v>
       </c>
-      <c r="E164" s="86"/>
+      <c r="E164" s="87"/>
       <c r="F164" s="6" t="s">
         <v>224</v>
       </c>
@@ -4243,15 +4243,15 @@
       <c r="H164" s="17"/>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="79"/>
+      <c r="A165" s="80"/>
       <c r="B165" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C165" s="86"/>
+      <c r="C165" s="87"/>
       <c r="D165" s="6">
         <v>0</v>
       </c>
-      <c r="E165" s="86"/>
+      <c r="E165" s="87"/>
       <c r="F165" s="6" t="s">
         <v>224</v>
       </c>
@@ -4259,15 +4259,15 @@
       <c r="H165" s="15"/>
     </row>
     <row r="166" spans="1:8">
-      <c r="A166" s="79"/>
+      <c r="A166" s="80"/>
       <c r="B166" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="C166" s="86"/>
+      <c r="C166" s="87"/>
       <c r="D166" s="6">
         <v>1</v>
       </c>
-      <c r="E166" s="86"/>
+      <c r="E166" s="87"/>
       <c r="F166" s="6" t="s">
         <v>226</v>
       </c>
@@ -4275,15 +4275,15 @@
       <c r="H166" s="30"/>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="79"/>
+      <c r="A167" s="80"/>
       <c r="B167" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C167" s="87"/>
+      <c r="C167" s="88"/>
       <c r="D167" s="6">
         <v>0</v>
       </c>
-      <c r="E167" s="87"/>
+      <c r="E167" s="88"/>
       <c r="F167" s="6" t="s">
         <v>224</v>
       </c>
@@ -4291,19 +4291,19 @@
       <c r="H167" s="15"/>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="79" t="s">
+      <c r="A168" s="80" t="s">
         <v>171</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C168" s="85">
+      <c r="C168" s="86">
         <v>1</v>
       </c>
       <c r="D168" s="6">
         <v>1</v>
       </c>
-      <c r="E168" s="85" t="s">
+      <c r="E168" s="86" t="s">
         <v>226</v>
       </c>
       <c r="F168" s="6" t="s">
@@ -4313,13 +4313,13 @@
       <c r="H168" s="3"/>
     </row>
     <row r="169" spans="1:8">
-      <c r="A169" s="79"/>
+      <c r="A169" s="80"/>
       <c r="B169" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="C169" s="87"/>
+      <c r="C169" s="88"/>
       <c r="D169" s="6"/>
-      <c r="E169" s="87"/>
+      <c r="E169" s="88"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
       <c r="H169" s="7"/>
@@ -4353,17 +4353,17 @@
       <c r="H171" s="7"/>
     </row>
     <row r="172" spans="1:8">
-      <c r="A172" s="80" t="s">
+      <c r="A172" s="81" t="s">
         <v>176</v>
       </c>
       <c r="B172" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C172" s="85">
+      <c r="C172" s="86">
         <v>2</v>
       </c>
       <c r="D172" s="6"/>
-      <c r="E172" s="85" t="s">
+      <c r="E172" s="86" t="s">
         <v>226</v>
       </c>
       <c r="F172" s="6"/>
@@ -4371,85 +4371,85 @@
       <c r="H172" s="15"/>
     </row>
     <row r="173" spans="1:8">
-      <c r="A173" s="80"/>
+      <c r="A173" s="81"/>
       <c r="B173" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C173" s="86"/>
+      <c r="C173" s="87"/>
       <c r="D173" s="6"/>
-      <c r="E173" s="86"/>
+      <c r="E173" s="87"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
       <c r="H173" s="7"/>
     </row>
     <row r="174" spans="1:8">
-      <c r="A174" s="80"/>
+      <c r="A174" s="81"/>
       <c r="B174" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C174" s="86"/>
+      <c r="C174" s="87"/>
       <c r="D174" s="6"/>
-      <c r="E174" s="86"/>
+      <c r="E174" s="87"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
       <c r="H174" s="7"/>
     </row>
     <row r="175" spans="1:8">
-      <c r="A175" s="80"/>
+      <c r="A175" s="81"/>
       <c r="B175" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C175" s="86"/>
+      <c r="C175" s="87"/>
       <c r="D175" s="6"/>
-      <c r="E175" s="86"/>
+      <c r="E175" s="87"/>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
       <c r="H175" s="7"/>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" s="80"/>
+      <c r="A176" s="81"/>
       <c r="B176" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C176" s="86"/>
+      <c r="C176" s="87"/>
       <c r="D176" s="6"/>
-      <c r="E176" s="86"/>
+      <c r="E176" s="87"/>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
       <c r="H176" s="7"/>
     </row>
     <row r="177" spans="1:8">
-      <c r="A177" s="80"/>
+      <c r="A177" s="81"/>
       <c r="B177" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C177" s="86"/>
+      <c r="C177" s="87"/>
       <c r="D177" s="6"/>
-      <c r="E177" s="86"/>
+      <c r="E177" s="87"/>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
       <c r="H177" s="7"/>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="80"/>
+      <c r="A178" s="81"/>
       <c r="B178" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C178" s="86"/>
+      <c r="C178" s="87"/>
       <c r="D178" s="6"/>
-      <c r="E178" s="86"/>
+      <c r="E178" s="87"/>
       <c r="F178" s="6"/>
       <c r="G178" s="6"/>
       <c r="H178" s="7"/>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="80"/>
+      <c r="A179" s="81"/>
       <c r="B179" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C179" s="87"/>
+      <c r="C179" s="88"/>
       <c r="D179" s="6"/>
-      <c r="E179" s="87"/>
+      <c r="E179" s="88"/>
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
       <c r="H179" s="7"/>
@@ -4525,319 +4525,319 @@
       <c r="H184" s="13"/>
     </row>
     <row r="185" spans="1:8">
-      <c r="A185" s="74" t="s">
+      <c r="A185" s="75" t="s">
         <v>193</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C185" s="85"/>
+      <c r="C185" s="86"/>
       <c r="D185" s="6"/>
-      <c r="E185" s="85"/>
+      <c r="E185" s="86"/>
       <c r="F185" s="6"/>
       <c r="G185" s="12"/>
       <c r="H185" s="13"/>
     </row>
     <row r="186" spans="1:8">
-      <c r="A186" s="74"/>
+      <c r="A186" s="75"/>
       <c r="B186" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C186" s="86"/>
+      <c r="C186" s="87"/>
       <c r="D186" s="6"/>
-      <c r="E186" s="86"/>
+      <c r="E186" s="87"/>
       <c r="F186" s="6"/>
       <c r="G186" s="12"/>
       <c r="H186" s="13"/>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="74"/>
+      <c r="A187" s="75"/>
       <c r="B187" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C187" s="86"/>
+      <c r="C187" s="87"/>
       <c r="D187" s="6"/>
-      <c r="E187" s="86"/>
+      <c r="E187" s="87"/>
       <c r="F187" s="6"/>
       <c r="G187" s="12"/>
       <c r="H187" s="13"/>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="74"/>
+      <c r="A188" s="75"/>
       <c r="B188" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C188" s="86"/>
+      <c r="C188" s="87"/>
       <c r="D188" s="6"/>
-      <c r="E188" s="86"/>
+      <c r="E188" s="87"/>
       <c r="F188" s="6"/>
       <c r="G188" s="12"/>
       <c r="H188" s="13"/>
     </row>
     <row r="189" spans="1:8">
-      <c r="A189" s="74"/>
+      <c r="A189" s="75"/>
       <c r="B189" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C189" s="86"/>
+      <c r="C189" s="87"/>
       <c r="D189" s="6"/>
-      <c r="E189" s="86"/>
+      <c r="E189" s="87"/>
       <c r="F189" s="6"/>
       <c r="G189" s="12"/>
       <c r="H189" s="13"/>
     </row>
     <row r="190" spans="1:8">
-      <c r="A190" s="74"/>
+      <c r="A190" s="75"/>
       <c r="B190" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C190" s="87"/>
+      <c r="C190" s="88"/>
       <c r="D190" s="6"/>
-      <c r="E190" s="87"/>
+      <c r="E190" s="88"/>
       <c r="F190" s="6"/>
       <c r="G190" s="12"/>
       <c r="H190" s="13"/>
     </row>
     <row r="191" spans="1:8">
-      <c r="A191" s="74" t="s">
+      <c r="A191" s="75" t="s">
         <v>200</v>
       </c>
       <c r="B191" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C191" s="85"/>
+      <c r="C191" s="86"/>
       <c r="D191" s="6"/>
-      <c r="E191" s="85"/>
+      <c r="E191" s="86"/>
       <c r="F191" s="6"/>
       <c r="G191" s="12"/>
       <c r="H191" s="13"/>
     </row>
     <row r="192" spans="1:8">
-      <c r="A192" s="74"/>
+      <c r="A192" s="75"/>
       <c r="B192" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C192" s="86"/>
+      <c r="C192" s="87"/>
       <c r="D192" s="6"/>
-      <c r="E192" s="86"/>
+      <c r="E192" s="87"/>
       <c r="F192" s="6"/>
       <c r="G192" s="12"/>
       <c r="H192" s="13"/>
     </row>
     <row r="193" spans="1:8">
-      <c r="A193" s="74"/>
+      <c r="A193" s="75"/>
       <c r="B193" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C193" s="86"/>
+      <c r="C193" s="87"/>
       <c r="D193" s="6"/>
-      <c r="E193" s="86"/>
+      <c r="E193" s="87"/>
       <c r="F193" s="6"/>
       <c r="G193" s="12"/>
       <c r="H193" s="13"/>
     </row>
     <row r="194" spans="1:8">
-      <c r="A194" s="74"/>
+      <c r="A194" s="75"/>
       <c r="B194" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C194" s="86"/>
+      <c r="C194" s="87"/>
       <c r="D194" s="6"/>
-      <c r="E194" s="86"/>
+      <c r="E194" s="87"/>
       <c r="F194" s="6"/>
       <c r="G194" s="12"/>
       <c r="H194" s="13"/>
     </row>
     <row r="195" spans="1:8">
-      <c r="A195" s="74"/>
+      <c r="A195" s="75"/>
       <c r="B195" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="C195" s="86"/>
+      <c r="C195" s="87"/>
       <c r="D195" s="6"/>
-      <c r="E195" s="86"/>
+      <c r="E195" s="87"/>
       <c r="F195" s="6"/>
       <c r="G195" s="12"/>
       <c r="H195" s="13"/>
     </row>
     <row r="196" spans="1:8">
-      <c r="A196" s="74"/>
+      <c r="A196" s="75"/>
       <c r="B196" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C196" s="86"/>
+      <c r="C196" s="87"/>
       <c r="D196" s="6"/>
-      <c r="E196" s="86"/>
+      <c r="E196" s="87"/>
       <c r="F196" s="6"/>
       <c r="G196" s="12"/>
       <c r="H196" s="13"/>
     </row>
     <row r="197" spans="1:8">
-      <c r="A197" s="74"/>
+      <c r="A197" s="75"/>
       <c r="B197" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C197" s="86"/>
+      <c r="C197" s="87"/>
       <c r="D197" s="6"/>
-      <c r="E197" s="86"/>
+      <c r="E197" s="87"/>
       <c r="F197" s="6"/>
       <c r="G197" s="12"/>
       <c r="H197" s="13"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="74"/>
+      <c r="A198" s="75"/>
       <c r="B198" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C198" s="86"/>
+      <c r="C198" s="87"/>
       <c r="D198" s="6"/>
-      <c r="E198" s="86"/>
+      <c r="E198" s="87"/>
       <c r="F198" s="6"/>
       <c r="G198" s="12"/>
       <c r="H198" s="13"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="74"/>
+      <c r="A199" s="75"/>
       <c r="B199" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C199" s="87"/>
+      <c r="C199" s="88"/>
       <c r="D199" s="6"/>
-      <c r="E199" s="87"/>
+      <c r="E199" s="88"/>
       <c r="F199" s="6"/>
       <c r="G199" s="12"/>
       <c r="H199" s="13"/>
     </row>
     <row r="200" spans="1:8">
-      <c r="A200" s="74" t="s">
+      <c r="A200" s="75" t="s">
         <v>210</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C200" s="85"/>
+      <c r="C200" s="86"/>
       <c r="D200" s="6"/>
-      <c r="E200" s="85"/>
+      <c r="E200" s="86"/>
       <c r="F200" s="6"/>
       <c r="G200" s="12"/>
       <c r="H200" s="13"/>
     </row>
     <row r="201" spans="1:8">
-      <c r="A201" s="74"/>
+      <c r="A201" s="75"/>
       <c r="B201" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="C201" s="86"/>
+      <c r="C201" s="87"/>
       <c r="D201" s="6"/>
-      <c r="E201" s="86"/>
+      <c r="E201" s="87"/>
       <c r="F201" s="6"/>
       <c r="G201" s="12"/>
       <c r="H201" s="13"/>
     </row>
     <row r="202" spans="1:8">
-      <c r="A202" s="74"/>
+      <c r="A202" s="75"/>
       <c r="B202" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C202" s="86"/>
+      <c r="C202" s="87"/>
       <c r="D202" s="6"/>
-      <c r="E202" s="86"/>
+      <c r="E202" s="87"/>
       <c r="F202" s="6"/>
       <c r="G202" s="12"/>
       <c r="H202" s="13"/>
     </row>
     <row r="203" spans="1:8">
-      <c r="A203" s="74"/>
+      <c r="A203" s="75"/>
       <c r="B203" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="C203" s="86"/>
+      <c r="C203" s="87"/>
       <c r="D203" s="6"/>
-      <c r="E203" s="86"/>
+      <c r="E203" s="87"/>
       <c r="F203" s="6"/>
       <c r="G203" s="12"/>
       <c r="H203" s="13"/>
     </row>
     <row r="204" spans="1:8">
-      <c r="A204" s="74"/>
+      <c r="A204" s="75"/>
       <c r="B204" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C204" s="86"/>
+      <c r="C204" s="87"/>
       <c r="D204" s="6"/>
-      <c r="E204" s="86"/>
+      <c r="E204" s="87"/>
       <c r="F204" s="6"/>
       <c r="G204" s="12"/>
       <c r="H204" s="13"/>
     </row>
     <row r="205" spans="1:8">
-      <c r="A205" s="74"/>
+      <c r="A205" s="75"/>
       <c r="B205" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="C205" s="86"/>
+      <c r="C205" s="87"/>
       <c r="D205" s="6"/>
-      <c r="E205" s="86"/>
+      <c r="E205" s="87"/>
       <c r="F205" s="6"/>
       <c r="G205" s="12"/>
       <c r="H205" s="13"/>
     </row>
     <row r="206" spans="1:8">
-      <c r="A206" s="74"/>
+      <c r="A206" s="75"/>
       <c r="B206" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C206" s="86"/>
+      <c r="C206" s="87"/>
       <c r="D206" s="6"/>
-      <c r="E206" s="86"/>
+      <c r="E206" s="87"/>
       <c r="F206" s="6"/>
       <c r="G206" s="12"/>
       <c r="H206" s="13"/>
     </row>
     <row r="207" spans="1:8">
-      <c r="A207" s="74"/>
+      <c r="A207" s="75"/>
       <c r="B207" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="C207" s="86"/>
+      <c r="C207" s="87"/>
       <c r="D207" s="6"/>
-      <c r="E207" s="86"/>
+      <c r="E207" s="87"/>
       <c r="F207" s="6"/>
       <c r="G207" s="12"/>
       <c r="H207" s="13"/>
     </row>
     <row r="208" spans="1:8">
-      <c r="A208" s="74"/>
+      <c r="A208" s="75"/>
       <c r="B208" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C208" s="86"/>
+      <c r="C208" s="87"/>
       <c r="D208" s="6"/>
-      <c r="E208" s="86"/>
+      <c r="E208" s="87"/>
       <c r="F208" s="6"/>
       <c r="G208" s="12"/>
       <c r="H208" s="13"/>
     </row>
     <row r="209" spans="1:8">
-      <c r="A209" s="74"/>
+      <c r="A209" s="75"/>
       <c r="B209" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C209" s="86"/>
+      <c r="C209" s="87"/>
       <c r="D209" s="6"/>
-      <c r="E209" s="86"/>
+      <c r="E209" s="87"/>
       <c r="F209" s="6"/>
       <c r="G209" s="12"/>
       <c r="H209" s="13"/>
     </row>
     <row r="210" spans="1:8">
-      <c r="A210" s="75"/>
+      <c r="A210" s="76"/>
       <c r="B210" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="C210" s="86"/>
+      <c r="C210" s="87"/>
       <c r="D210" s="18"/>
-      <c r="E210" s="86"/>
+      <c r="E210" s="87"/>
       <c r="F210" s="18"/>
       <c r="G210" s="20"/>
       <c r="H210" s="21"/>
@@ -4865,19 +4865,19 @@
       <c r="H211" s="24"/>
     </row>
     <row r="212" spans="1:8">
-      <c r="A212" s="61" t="s">
+      <c r="A212" s="62" t="s">
         <v>231</v>
       </c>
       <c r="B212" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="C212" s="63">
+      <c r="C212" s="64">
         <v>3</v>
       </c>
       <c r="D212" s="46">
         <v>3</v>
       </c>
-      <c r="E212" s="63" t="s">
+      <c r="E212" s="64" t="s">
         <v>253</v>
       </c>
       <c r="F212" s="46" t="s">
@@ -4887,39 +4887,39 @@
       <c r="H212" s="53"/>
     </row>
     <row r="213" spans="1:8">
-      <c r="A213" s="62"/>
+      <c r="A213" s="63"/>
       <c r="B213" s="22" t="s">
         <v>257</v>
       </c>
-      <c r="C213" s="64"/>
+      <c r="C213" s="65"/>
       <c r="D213" s="23"/>
-      <c r="E213" s="64"/>
+      <c r="E213" s="65"/>
       <c r="F213" s="23"/>
       <c r="G213" s="23"/>
       <c r="H213" s="22"/>
     </row>
     <row r="214" spans="1:8">
-      <c r="A214" s="65" t="s">
+      <c r="A214" s="66" t="s">
         <v>233</v>
       </c>
       <c r="B214" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="C214" s="66"/>
+      <c r="C214" s="67"/>
       <c r="D214" s="23"/>
-      <c r="E214" s="66"/>
+      <c r="E214" s="67"/>
       <c r="F214" s="23"/>
       <c r="G214" s="24"/>
       <c r="H214" s="24"/>
     </row>
     <row r="215" spans="1:8">
-      <c r="A215" s="65"/>
+      <c r="A215" s="66"/>
       <c r="B215" s="50" t="s">
         <v>235</v>
       </c>
-      <c r="C215" s="67"/>
+      <c r="C215" s="68"/>
       <c r="D215" s="51"/>
-      <c r="E215" s="67"/>
+      <c r="E215" s="68"/>
       <c r="F215" s="51"/>
       <c r="G215" s="52"/>
       <c r="H215" s="52"/>

--- a/Study.xlsx
+++ b/Study.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\DH_Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DFC29F3-7BDE-4B3E-9DEA-87CAC63C5B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F138E4E-95E9-4579-8A62-3DBA76A9E574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,7 +897,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -917,14 +917,6 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -972,17 +964,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1244,12 +1231,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1258,11 +1245,8 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1270,121 +1254,118 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1396,41 +1377,101 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1439,7 +1480,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1448,73 +1489,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Accent3" xfId="5" builtinId="37"/>
-    <cellStyle name="Bad" xfId="4" builtinId="27"/>
-    <cellStyle name="Good" xfId="3" builtinId="26"/>
-    <cellStyle name="Input" xfId="2" builtinId="20"/>
-    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
+  <cellStyles count="5">
+    <cellStyle name="Accent3" xfId="4" builtinId="37"/>
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
+    <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1825,14 +1805,14 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="67" t="s">
         <v>221</v>
       </c>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82" t="s">
+      <c r="D1" s="67"/>
+      <c r="E1" s="67" t="s">
         <v>225</v>
       </c>
-      <c r="F1" s="82"/>
+      <c r="F1" s="67"/>
       <c r="G1" s="4" t="s">
         <v>222</v>
       </c>
@@ -1841,1159 +1821,1159 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="79" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="83">
+      <c r="C2" s="64">
         <v>0</v>
       </c>
       <c r="D2" s="6">
         <v>0</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="64" t="s">
         <v>224</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="17"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="69"/>
+      <c r="A3" s="79"/>
       <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="83"/>
+      <c r="C3" s="64"/>
       <c r="D3" s="6">
         <v>0</v>
       </c>
-      <c r="E3" s="83"/>
+      <c r="E3" s="64"/>
       <c r="F3" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="17"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="69"/>
+      <c r="A4" s="79"/>
       <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="83"/>
+      <c r="C4" s="64"/>
       <c r="D4" s="6">
         <v>0</v>
       </c>
-      <c r="E4" s="83"/>
+      <c r="E4" s="64"/>
       <c r="F4" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="17"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="16"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="69"/>
+      <c r="A5" s="79"/>
       <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="83"/>
+      <c r="C5" s="64"/>
       <c r="D5" s="6">
         <v>0</v>
       </c>
-      <c r="E5" s="83"/>
+      <c r="E5" s="64"/>
       <c r="F5" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="69"/>
+      <c r="A6" s="79"/>
       <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="83"/>
+      <c r="C6" s="64"/>
       <c r="D6" s="6">
         <v>0</v>
       </c>
-      <c r="E6" s="83"/>
+      <c r="E6" s="64"/>
       <c r="F6" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="69"/>
+      <c r="A7" s="79"/>
       <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="83"/>
+      <c r="C7" s="64"/>
       <c r="D7" s="6">
         <v>0</v>
       </c>
-      <c r="E7" s="83"/>
+      <c r="E7" s="64"/>
       <c r="F7" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="69"/>
+      <c r="A8" s="79"/>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="83"/>
+      <c r="C8" s="64"/>
       <c r="D8" s="6">
         <v>0</v>
       </c>
-      <c r="E8" s="83"/>
+      <c r="E8" s="64"/>
       <c r="F8" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="79" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="83">
+      <c r="C9" s="64">
         <v>0</v>
       </c>
       <c r="D9" s="6">
         <v>0</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="64" t="s">
         <v>224</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="14"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="69"/>
+      <c r="A10" s="79"/>
       <c r="B10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="83"/>
+      <c r="C10" s="64"/>
       <c r="D10" s="6">
         <v>0</v>
       </c>
-      <c r="E10" s="83"/>
+      <c r="E10" s="64"/>
       <c r="F10" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="15"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="14"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="69"/>
+      <c r="A11" s="79"/>
       <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="83"/>
+      <c r="C11" s="64"/>
       <c r="D11" s="6">
         <v>0</v>
       </c>
-      <c r="E11" s="83"/>
+      <c r="E11" s="64"/>
       <c r="F11" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="17"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="16"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="69"/>
+      <c r="A12" s="79"/>
       <c r="B12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="83"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="6">
         <v>0</v>
       </c>
-      <c r="E12" s="83"/>
+      <c r="E12" s="64"/>
       <c r="F12" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="16"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="69"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="83"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="6">
         <v>0</v>
       </c>
-      <c r="E13" s="83"/>
+      <c r="E13" s="64"/>
       <c r="F13" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="16"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="69"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="83"/>
+      <c r="C14" s="64"/>
       <c r="D14" s="6">
         <v>0</v>
       </c>
-      <c r="E14" s="83"/>
+      <c r="E14" s="64"/>
       <c r="F14" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="17"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="16"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="69"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="83"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="6">
         <v>0</v>
       </c>
-      <c r="E15" s="83"/>
+      <c r="E15" s="64"/>
       <c r="F15" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="17"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="16"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="69"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="83"/>
+      <c r="C16" s="64"/>
       <c r="D16" s="6">
         <v>0</v>
       </c>
-      <c r="E16" s="83"/>
+      <c r="E16" s="64"/>
       <c r="F16" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="17"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="16"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="69" t="s">
+      <c r="A17" s="79" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="83">
+      <c r="C17" s="64">
         <v>0</v>
       </c>
       <c r="D17" s="6">
         <v>0</v>
       </c>
-      <c r="E17" s="83" t="s">
+      <c r="E17" s="64" t="s">
         <v>224</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="17"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="69"/>
+      <c r="A18" s="79"/>
       <c r="B18" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="83"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="6">
         <v>0</v>
       </c>
-      <c r="E18" s="83"/>
+      <c r="E18" s="64"/>
       <c r="F18" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="17"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="69"/>
+      <c r="A19" s="79"/>
       <c r="B19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="83"/>
+      <c r="C19" s="64"/>
       <c r="D19" s="6">
         <v>0</v>
       </c>
-      <c r="E19" s="83"/>
-      <c r="F19" s="58" t="s">
+      <c r="E19" s="64"/>
+      <c r="F19" s="57" t="s">
         <v>224</v>
       </c>
-      <c r="G19" s="45"/>
-      <c r="H19" s="61"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="60"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="69"/>
+      <c r="A20" s="79"/>
       <c r="B20" t="s">
         <v>254</v>
       </c>
-      <c r="C20" s="83"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="2">
         <v>0</v>
       </c>
-      <c r="E20" s="84"/>
-      <c r="F20" s="60" t="s">
+      <c r="E20" s="65"/>
+      <c r="F20" s="59" t="s">
         <v>224</v>
       </c>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="69" t="s">
+      <c r="A21" s="79" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="83">
+      <c r="C21" s="64">
         <v>0</v>
       </c>
       <c r="D21" s="6">
         <v>0</v>
       </c>
-      <c r="E21" s="84" t="s">
+      <c r="E21" s="65" t="s">
         <v>224</v>
       </c>
-      <c r="F21" s="40" t="s">
+      <c r="F21" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="69"/>
+      <c r="A22" s="79"/>
       <c r="B22" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="83"/>
+      <c r="C22" s="64"/>
       <c r="D22" s="6">
         <v>0</v>
       </c>
-      <c r="E22" s="84"/>
-      <c r="F22" s="40" t="s">
+      <c r="E22" s="65"/>
+      <c r="F22" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="69"/>
+      <c r="A23" s="79"/>
       <c r="B23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="83"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="6">
         <v>0</v>
       </c>
-      <c r="E23" s="83"/>
-      <c r="F23" s="59" t="s">
+      <c r="E23" s="64"/>
+      <c r="F23" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="G23" s="59"/>
-      <c r="H23" s="32"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="31"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="69"/>
+      <c r="A24" s="79"/>
       <c r="B24" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="83"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="6">
         <v>0</v>
       </c>
-      <c r="E24" s="83"/>
+      <c r="E24" s="64"/>
       <c r="F24" s="6" t="s">
         <v>226</v>
       </c>
       <c r="G24" s="6"/>
-      <c r="H24" s="17"/>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="69"/>
+      <c r="A25" s="79"/>
       <c r="B25" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="83"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="6">
         <v>0</v>
       </c>
-      <c r="E25" s="83"/>
+      <c r="E25" s="64"/>
       <c r="F25" s="6" t="s">
         <v>227</v>
       </c>
       <c r="G25" s="6"/>
-      <c r="H25" s="17"/>
+      <c r="H25" s="16"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="69" t="s">
+      <c r="A26" s="79" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C26" s="83">
+      <c r="C26" s="64">
         <v>0</v>
       </c>
       <c r="D26" s="6">
         <v>0</v>
       </c>
-      <c r="E26" s="83" t="s">
+      <c r="E26" s="64" t="s">
         <v>224</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G26" s="14"/>
-      <c r="H26" s="15"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="14"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="69"/>
+      <c r="A27" s="79"/>
       <c r="B27" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="83"/>
+      <c r="C27" s="64"/>
       <c r="D27" s="6">
         <v>0</v>
       </c>
-      <c r="E27" s="83"/>
+      <c r="E27" s="64"/>
       <c r="F27" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G27" s="16"/>
-      <c r="H27" s="17"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="69"/>
+      <c r="A28" s="79"/>
       <c r="B28" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="83"/>
+      <c r="C28" s="64"/>
       <c r="D28" s="6">
         <v>0</v>
       </c>
-      <c r="E28" s="83"/>
+      <c r="E28" s="64"/>
       <c r="F28" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G28" s="16"/>
-      <c r="H28" s="17"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="16"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="69"/>
+      <c r="A29" s="79"/>
       <c r="B29" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="83"/>
+      <c r="C29" s="64"/>
       <c r="D29" s="6">
         <v>0</v>
       </c>
-      <c r="E29" s="83"/>
+      <c r="E29" s="64"/>
       <c r="F29" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G29" s="16"/>
-      <c r="H29" s="17"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="69"/>
+      <c r="A30" s="79"/>
       <c r="B30" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="83"/>
+      <c r="C30" s="64"/>
       <c r="D30" s="6">
         <v>0</v>
       </c>
-      <c r="E30" s="83"/>
+      <c r="E30" s="64"/>
       <c r="F30" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G30" s="16"/>
-      <c r="H30" s="17"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="16"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="69"/>
+      <c r="A31" s="79"/>
       <c r="B31" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="83"/>
+      <c r="C31" s="64"/>
       <c r="D31" s="6">
         <v>0</v>
       </c>
-      <c r="E31" s="83"/>
+      <c r="E31" s="64"/>
       <c r="F31" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G31" s="16"/>
-      <c r="H31" s="17"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="69"/>
+      <c r="A32" s="79"/>
       <c r="B32" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="83"/>
+      <c r="C32" s="64"/>
       <c r="D32" s="6">
         <v>0</v>
       </c>
-      <c r="E32" s="83"/>
+      <c r="E32" s="64"/>
       <c r="F32" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G32" s="16"/>
-      <c r="H32" s="17"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="16"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="69"/>
+      <c r="A33" s="79"/>
       <c r="B33" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="83"/>
+      <c r="C33" s="64"/>
       <c r="D33" s="6">
         <v>0</v>
       </c>
-      <c r="E33" s="83"/>
+      <c r="E33" s="64"/>
       <c r="F33" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="7"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="16"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="69" t="s">
+      <c r="A34" s="79" t="s">
         <v>38</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="83">
+      <c r="C34" s="64">
         <v>1</v>
       </c>
       <c r="D34" s="6">
         <v>1</v>
       </c>
-      <c r="E34" s="83" t="s">
+      <c r="E34" s="64" t="s">
         <v>224</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>224</v>
       </c>
       <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
+      <c r="H34"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="69"/>
+      <c r="A35" s="79"/>
       <c r="B35" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="83"/>
+      <c r="C35" s="64"/>
       <c r="D35" s="6">
         <v>1</v>
       </c>
-      <c r="E35" s="83"/>
+      <c r="E35" s="64"/>
       <c r="F35" s="6" t="s">
         <v>224</v>
       </c>
       <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
+      <c r="H35"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="69"/>
+      <c r="A36" s="79"/>
       <c r="B36" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="83"/>
+      <c r="C36" s="64"/>
       <c r="D36" s="6">
         <v>1</v>
       </c>
-      <c r="E36" s="83"/>
+      <c r="E36" s="64"/>
       <c r="F36" s="6" t="s">
         <v>224</v>
       </c>
       <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
+      <c r="H36"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="69"/>
-      <c r="B37" s="26" t="s">
+      <c r="A37" s="79"/>
+      <c r="B37" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="83"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
       <c r="H37"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="70"/>
-      <c r="B38" s="22" t="s">
+      <c r="A38" s="80"/>
+      <c r="B38" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="C38" s="85"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="22"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="21"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="70"/>
-      <c r="B39" s="28" t="s">
+      <c r="A39" s="80"/>
+      <c r="B39" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="C39" s="85"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="83"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="22"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="21"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="70"/>
-      <c r="B40" s="28" t="s">
+      <c r="A40" s="80"/>
+      <c r="B40" s="27" t="s">
         <v>238</v>
       </c>
-      <c r="C40" s="85"/>
+      <c r="C40" s="66"/>
       <c r="D40" s="6"/>
-      <c r="E40" s="83"/>
+      <c r="E40" s="64"/>
       <c r="F40" s="6"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="22"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="21"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="72" t="s">
+      <c r="A41" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="C41" s="83">
+      <c r="C41" s="64">
         <v>1</v>
       </c>
       <c r="D41" s="6">
         <v>0</v>
       </c>
-      <c r="E41" s="83" t="s">
+      <c r="E41" s="64" t="s">
         <v>226</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G41" s="16"/>
-      <c r="H41" s="32"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="31"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="72"/>
+      <c r="A42" s="76"/>
       <c r="B42" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="83"/>
+      <c r="C42" s="64"/>
       <c r="D42" s="6">
         <v>1</v>
       </c>
-      <c r="E42" s="83"/>
+      <c r="E42" s="64"/>
       <c r="F42" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G42" s="16"/>
-      <c r="H42" s="17"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="72"/>
+      <c r="A43" s="76"/>
       <c r="B43" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="83"/>
+      <c r="C43" s="64"/>
       <c r="D43" s="6">
         <v>1</v>
       </c>
-      <c r="E43" s="83"/>
+      <c r="E43" s="64"/>
       <c r="F43" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G43" s="16"/>
-      <c r="H43" s="17"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="72"/>
+      <c r="A44" s="76"/>
       <c r="B44" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="83"/>
+      <c r="C44" s="64"/>
       <c r="D44" s="6">
         <v>1</v>
       </c>
-      <c r="E44" s="83"/>
+      <c r="E44" s="64"/>
       <c r="F44" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G44" s="16"/>
-      <c r="H44" s="17"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="72"/>
+      <c r="A45" s="76"/>
       <c r="B45" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="83"/>
+      <c r="C45" s="64"/>
       <c r="D45" s="6">
         <v>1</v>
       </c>
-      <c r="E45" s="83"/>
+      <c r="E45" s="64"/>
       <c r="F45" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G45" s="16"/>
-      <c r="H45" s="17"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="72"/>
+      <c r="A46" s="76"/>
       <c r="B46" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="C46" s="83"/>
+      <c r="C46" s="64"/>
       <c r="D46" s="6">
         <v>1</v>
       </c>
-      <c r="E46" s="83"/>
+      <c r="E46" s="64"/>
       <c r="F46" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G46" s="44"/>
-      <c r="H46" s="17"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="16"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="72"/>
+      <c r="A47" s="76"/>
       <c r="B47" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C47" s="83"/>
+      <c r="C47" s="64"/>
       <c r="D47" s="6">
         <v>1</v>
       </c>
-      <c r="E47" s="83"/>
+      <c r="E47" s="64"/>
       <c r="F47" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G47" s="16"/>
-      <c r="H47" s="17"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="16"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="72" t="s">
+      <c r="A48" s="76" t="s">
         <v>48</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="83">
+      <c r="C48" s="64">
         <v>2</v>
       </c>
       <c r="D48" s="6">
         <v>0</v>
       </c>
-      <c r="E48" s="83" t="s">
+      <c r="E48" s="64" t="s">
         <v>226</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G48" s="16"/>
-      <c r="H48" s="17"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="16"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="72"/>
+      <c r="A49" s="76"/>
       <c r="B49" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="83"/>
+      <c r="C49" s="64"/>
       <c r="D49" s="6">
         <v>2</v>
       </c>
-      <c r="E49" s="83"/>
+      <c r="E49" s="64"/>
       <c r="F49" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G49" s="16"/>
-      <c r="H49" s="17"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="16"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="72"/>
+      <c r="A50" s="76"/>
       <c r="B50" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C50" s="83"/>
+      <c r="C50" s="64"/>
       <c r="D50" s="6">
         <v>2</v>
       </c>
-      <c r="E50" s="83"/>
+      <c r="E50" s="64"/>
       <c r="F50" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G50" s="16"/>
-      <c r="H50" s="17"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="16"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="72"/>
+      <c r="A51" s="76"/>
       <c r="B51" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C51" s="83"/>
+      <c r="C51" s="64"/>
       <c r="D51" s="6">
         <v>2</v>
       </c>
-      <c r="E51" s="83"/>
+      <c r="E51" s="64"/>
       <c r="F51" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G51" s="16"/>
-      <c r="H51" s="17"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="16"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="72"/>
+      <c r="A52" s="76"/>
       <c r="B52" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C52" s="83"/>
+      <c r="C52" s="64"/>
       <c r="D52" s="6">
         <v>2</v>
       </c>
-      <c r="E52" s="83"/>
+      <c r="E52" s="64"/>
       <c r="F52" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G52" s="16"/>
-      <c r="H52" s="17"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="16"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="72" t="s">
+      <c r="A53" s="76" t="s">
         <v>241</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="83">
+      <c r="C53" s="64">
         <v>2</v>
       </c>
       <c r="D53" s="6">
         <v>0</v>
       </c>
-      <c r="E53" s="83" t="s">
+      <c r="E53" s="64" t="s">
         <v>227</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G53" s="16"/>
-      <c r="H53" s="11"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="72"/>
+      <c r="A54" s="76"/>
       <c r="B54" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C54" s="83"/>
+      <c r="C54" s="64"/>
       <c r="D54" s="6">
         <v>2</v>
       </c>
-      <c r="E54" s="83"/>
+      <c r="E54" s="64"/>
       <c r="F54" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G54" s="16"/>
-      <c r="H54" s="11"/>
+      <c r="G54" s="15"/>
+      <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="72"/>
+      <c r="A55" s="76"/>
       <c r="B55" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C55" s="83"/>
+      <c r="C55" s="64"/>
       <c r="D55" s="6">
         <v>2</v>
       </c>
-      <c r="E55" s="83"/>
+      <c r="E55" s="64"/>
       <c r="F55" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G55" s="16"/>
-      <c r="H55" s="11"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="72"/>
+      <c r="A56" s="76"/>
       <c r="B56" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C56" s="83"/>
+      <c r="C56" s="64"/>
       <c r="D56" s="6">
         <v>2</v>
       </c>
-      <c r="E56" s="83"/>
+      <c r="E56" s="64"/>
       <c r="F56" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G56" s="16"/>
-      <c r="H56" s="10"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="9"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="72"/>
+      <c r="A57" s="76"/>
       <c r="B57" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="C57" s="83"/>
+      <c r="C57" s="64"/>
       <c r="D57" s="6">
         <v>2</v>
       </c>
-      <c r="E57" s="83"/>
+      <c r="E57" s="64"/>
       <c r="F57" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G57" s="16"/>
-      <c r="H57" s="11"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="10"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="72"/>
+      <c r="A58" s="76"/>
       <c r="B58" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="C58" s="83"/>
+      <c r="C58" s="64"/>
       <c r="D58" s="6">
         <v>2</v>
       </c>
-      <c r="E58" s="83"/>
-      <c r="F58" s="37" t="s">
+      <c r="E58" s="64"/>
+      <c r="F58" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="G58" s="45"/>
-      <c r="H58" s="43"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="42"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="72"/>
+      <c r="A59" s="76"/>
       <c r="B59" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C59" s="83"/>
+      <c r="C59" s="64"/>
       <c r="D59" s="6">
         <v>0</v>
       </c>
-      <c r="E59" s="84"/>
-      <c r="F59" s="40" t="s">
+      <c r="E59" s="65"/>
+      <c r="F59" s="39" t="s">
         <v>227</v>
       </c>
-      <c r="G59" s="41"/>
-      <c r="H59" s="42"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="41"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="72"/>
+      <c r="A60" s="76"/>
       <c r="B60" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="C60" s="83"/>
-      <c r="D60" s="38">
+      <c r="C60" s="64"/>
+      <c r="D60" s="37">
         <v>2</v>
       </c>
-      <c r="E60" s="84"/>
-      <c r="F60" s="39" t="s">
+      <c r="E60" s="65"/>
+      <c r="F60" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="G60" s="41"/>
-      <c r="H60" s="42"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="41"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="72" t="s">
+      <c r="A61" s="76" t="s">
         <v>55</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C61" s="83">
+      <c r="C61" s="64">
         <v>2</v>
       </c>
       <c r="D61" s="6">
         <v>2</v>
       </c>
-      <c r="E61" s="83" t="s">
+      <c r="E61" s="64" t="s">
         <v>227</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G61" s="31"/>
-      <c r="H61" s="32"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="31"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="72"/>
+      <c r="A62" s="76"/>
       <c r="B62" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="83"/>
+      <c r="C62" s="64"/>
       <c r="D62" s="6">
         <v>2</v>
       </c>
-      <c r="E62" s="83"/>
+      <c r="E62" s="64"/>
       <c r="F62" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G62" s="16"/>
-      <c r="H62" s="17"/>
+      <c r="G62" s="15"/>
+      <c r="H62" s="16"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="72"/>
+      <c r="A63" s="76"/>
       <c r="B63" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C63" s="83"/>
+      <c r="C63" s="64"/>
       <c r="D63" s="6">
         <v>2</v>
       </c>
-      <c r="E63" s="83"/>
+      <c r="E63" s="64"/>
       <c r="F63" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G63" s="16"/>
-      <c r="H63" s="17"/>
+      <c r="G63" s="15"/>
+      <c r="H63" s="16"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="72"/>
+      <c r="A64" s="76"/>
       <c r="B64" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C64" s="83"/>
+      <c r="C64" s="64"/>
       <c r="D64" s="6">
         <v>2</v>
       </c>
-      <c r="E64" s="83"/>
+      <c r="E64" s="64"/>
       <c r="F64" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G64" s="16"/>
-      <c r="H64" s="17"/>
+      <c r="G64" s="15"/>
+      <c r="H64" s="16"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="72"/>
+      <c r="A65" s="76"/>
       <c r="B65" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C65" s="83"/>
+      <c r="C65" s="64"/>
       <c r="D65" s="6">
         <v>2</v>
       </c>
-      <c r="E65" s="83"/>
+      <c r="E65" s="64"/>
       <c r="F65" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G65" s="16"/>
-      <c r="H65" s="30"/>
+      <c r="G65" s="15"/>
+      <c r="H65" s="29"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="72"/>
+      <c r="A66" s="76"/>
       <c r="B66" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C66" s="83"/>
+      <c r="C66" s="64"/>
       <c r="D66" s="6">
         <v>2</v>
       </c>
-      <c r="E66" s="83"/>
+      <c r="E66" s="64"/>
       <c r="F66" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G66" s="16"/>
-      <c r="H66" s="30"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="29"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="73" t="s">
+      <c r="A67" s="77" t="s">
         <v>61</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C67" s="83">
+      <c r="C67" s="64">
         <v>2</v>
       </c>
       <c r="D67" s="6">
         <v>2</v>
       </c>
-      <c r="E67" s="83" t="s">
+      <c r="E67" s="64" t="s">
         <v>226</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G67" s="16"/>
-      <c r="H67" s="17"/>
+      <c r="G67" s="15"/>
+      <c r="H67" s="16"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="73"/>
+      <c r="A68" s="77"/>
       <c r="B68" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C68" s="83"/>
+      <c r="C68" s="64"/>
       <c r="D68" s="6">
         <v>2</v>
       </c>
-      <c r="E68" s="83"/>
+      <c r="E68" s="64"/>
       <c r="F68" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G68" s="16"/>
-      <c r="H68" s="17"/>
+      <c r="G68" s="15"/>
+      <c r="H68" s="16"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="74" t="s">
+      <c r="A69" s="78" t="s">
         <v>239</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="86">
+      <c r="C69" s="61">
         <v>2</v>
       </c>
       <c r="D69" s="6">
         <v>0</v>
       </c>
-      <c r="E69" s="86" t="s">
+      <c r="E69" s="61" t="s">
         <v>226</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G69" s="14"/>
-      <c r="H69" s="15"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="14"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="74"/>
+      <c r="A70" s="78"/>
       <c r="B70" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C70" s="87"/>
+      <c r="C70" s="62"/>
       <c r="D70" s="6">
         <v>0</v>
       </c>
-      <c r="E70" s="87"/>
+      <c r="E70" s="62"/>
       <c r="F70" s="6" t="s">
         <v>227</v>
       </c>
@@ -3001,729 +2981,729 @@
       <c r="H70"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="74"/>
+      <c r="A71" s="78"/>
       <c r="B71" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="87"/>
+      <c r="C71" s="62"/>
       <c r="D71" s="6"/>
-      <c r="E71" s="87"/>
+      <c r="E71" s="62"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="7"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="74"/>
+      <c r="A72" s="78"/>
       <c r="B72" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C72" s="87"/>
+      <c r="C72" s="62"/>
       <c r="D72" s="6"/>
-      <c r="E72" s="87"/>
+      <c r="E72" s="62"/>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
       <c r="H72" s="7"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="74"/>
+      <c r="A73" s="78"/>
       <c r="B73" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C73" s="87"/>
+      <c r="C73" s="62"/>
       <c r="D73" s="6"/>
-      <c r="E73" s="87"/>
+      <c r="E73" s="62"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="7"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="74"/>
+      <c r="A74" s="78"/>
       <c r="B74" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C74" s="87"/>
+      <c r="C74" s="62"/>
       <c r="D74" s="6"/>
-      <c r="E74" s="87"/>
+      <c r="E74" s="62"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
       <c r="H74" s="7"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="74"/>
+      <c r="A75" s="78"/>
       <c r="B75" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="87"/>
+      <c r="C75" s="62"/>
       <c r="D75" s="6"/>
-      <c r="E75" s="87"/>
+      <c r="E75" s="62"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
       <c r="H75" s="7"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="74"/>
+      <c r="A76" s="78"/>
       <c r="B76" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C76" s="87"/>
+      <c r="C76" s="62"/>
       <c r="D76" s="6"/>
-      <c r="E76" s="87"/>
+      <c r="E76" s="62"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="7"/>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="74"/>
+      <c r="A77" s="78"/>
       <c r="B77" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C77" s="87"/>
+      <c r="C77" s="62"/>
       <c r="D77" s="6"/>
-      <c r="E77" s="87"/>
+      <c r="E77" s="62"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
       <c r="H77" s="7"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="74"/>
+      <c r="A78" s="78"/>
       <c r="B78" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C78" s="87"/>
+      <c r="C78" s="62"/>
       <c r="D78" s="6"/>
-      <c r="E78" s="87"/>
+      <c r="E78" s="62"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
       <c r="H78" s="7"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="74"/>
+      <c r="A79" s="78"/>
       <c r="B79" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C79" s="87"/>
+      <c r="C79" s="62"/>
       <c r="D79" s="6"/>
-      <c r="E79" s="87"/>
+      <c r="E79" s="62"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="7"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="74"/>
+      <c r="A80" s="78"/>
       <c r="B80" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C80" s="88"/>
+      <c r="C80" s="63"/>
       <c r="D80" s="6"/>
-      <c r="E80" s="88"/>
+      <c r="E80" s="63"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="7"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="74" t="s">
+      <c r="A81" s="78" t="s">
         <v>76</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C81" s="86"/>
+      <c r="C81" s="61"/>
       <c r="D81" s="6"/>
-      <c r="E81" s="86"/>
+      <c r="E81" s="61"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="7"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="74"/>
+      <c r="A82" s="78"/>
       <c r="B82" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C82" s="87"/>
+      <c r="C82" s="62"/>
       <c r="D82" s="6"/>
-      <c r="E82" s="87"/>
+      <c r="E82" s="62"/>
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
       <c r="H82" s="7"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="74"/>
+      <c r="A83" s="78"/>
       <c r="B83" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C83" s="87"/>
+      <c r="C83" s="62"/>
       <c r="D83" s="6"/>
-      <c r="E83" s="87"/>
+      <c r="E83" s="62"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
       <c r="H83" s="7"/>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="74"/>
+      <c r="A84" s="78"/>
       <c r="B84" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C84" s="87"/>
+      <c r="C84" s="62"/>
       <c r="D84" s="6"/>
-      <c r="E84" s="87"/>
+      <c r="E84" s="62"/>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
       <c r="H84" s="7"/>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="74"/>
+      <c r="A85" s="78"/>
       <c r="B85" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C85" s="87"/>
+      <c r="C85" s="62"/>
       <c r="D85" s="6"/>
-      <c r="E85" s="87"/>
+      <c r="E85" s="62"/>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
       <c r="H85" s="7"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="74"/>
+      <c r="A86" s="78"/>
       <c r="B86" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C86" s="87"/>
+      <c r="C86" s="62"/>
       <c r="D86" s="6"/>
-      <c r="E86" s="87"/>
+      <c r="E86" s="62"/>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
       <c r="H86" s="7"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="74"/>
+      <c r="A87" s="78"/>
       <c r="B87" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C87" s="87"/>
+      <c r="C87" s="62"/>
       <c r="D87" s="6"/>
-      <c r="E87" s="87"/>
+      <c r="E87" s="62"/>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="7"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="74"/>
+      <c r="A88" s="78"/>
       <c r="B88" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C88" s="87"/>
+      <c r="C88" s="62"/>
       <c r="D88" s="6"/>
-      <c r="E88" s="87"/>
+      <c r="E88" s="62"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="7"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="74"/>
+      <c r="A89" s="78"/>
       <c r="B89" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C89" s="88"/>
+      <c r="C89" s="63"/>
       <c r="D89" s="6"/>
-      <c r="E89" s="88"/>
+      <c r="E89" s="63"/>
       <c r="F89" s="6"/>
-      <c r="G89" s="12"/>
-      <c r="H89" s="13"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="12"/>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="74" t="s">
+      <c r="A90" s="78" t="s">
         <v>86</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C90" s="86"/>
+      <c r="C90" s="61"/>
       <c r="D90" s="6"/>
-      <c r="E90" s="86"/>
+      <c r="E90" s="61"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
       <c r="H90" s="7"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="74"/>
+      <c r="A91" s="78"/>
       <c r="B91" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C91" s="87"/>
+      <c r="C91" s="62"/>
       <c r="D91" s="6"/>
-      <c r="E91" s="87"/>
+      <c r="E91" s="62"/>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
       <c r="H91" s="7"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="74"/>
+      <c r="A92" s="78"/>
       <c r="B92" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C92" s="87"/>
+      <c r="C92" s="62"/>
       <c r="D92" s="6"/>
-      <c r="E92" s="87"/>
+      <c r="E92" s="62"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
       <c r="H92" s="7"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="74"/>
+      <c r="A93" s="78"/>
       <c r="B93" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C93" s="87"/>
+      <c r="C93" s="62"/>
       <c r="D93" s="6"/>
-      <c r="E93" s="87"/>
+      <c r="E93" s="62"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
       <c r="H93" s="7"/>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="74"/>
+      <c r="A94" s="78"/>
       <c r="B94" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C94" s="87"/>
+      <c r="C94" s="62"/>
       <c r="D94" s="6"/>
-      <c r="E94" s="87"/>
+      <c r="E94" s="62"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="7"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="74"/>
+      <c r="A95" s="78"/>
       <c r="B95" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C95" s="87"/>
+      <c r="C95" s="62"/>
       <c r="D95" s="6"/>
-      <c r="E95" s="87"/>
+      <c r="E95" s="62"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
       <c r="H95" s="7"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="74"/>
+      <c r="A96" s="78"/>
       <c r="B96" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C96" s="87"/>
+      <c r="C96" s="62"/>
       <c r="D96" s="6"/>
-      <c r="E96" s="87"/>
+      <c r="E96" s="62"/>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="7"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="74"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C97" s="87"/>
+      <c r="C97" s="62"/>
       <c r="D97" s="6"/>
-      <c r="E97" s="87"/>
+      <c r="E97" s="62"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="7"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="74"/>
+      <c r="A98" s="78"/>
       <c r="B98" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C98" s="88"/>
+      <c r="C98" s="63"/>
       <c r="D98" s="6"/>
-      <c r="E98" s="88"/>
+      <c r="E98" s="63"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="7"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="74" t="s">
+      <c r="A99" s="78" t="s">
         <v>96</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C99" s="86"/>
+      <c r="C99" s="61"/>
       <c r="D99" s="6"/>
-      <c r="E99" s="86"/>
+      <c r="E99" s="61"/>
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="7"/>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="74"/>
+      <c r="A100" s="78"/>
       <c r="B100" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C100" s="87"/>
+      <c r="C100" s="62"/>
       <c r="D100" s="6"/>
-      <c r="E100" s="87"/>
+      <c r="E100" s="62"/>
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
       <c r="H100" s="7"/>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="74"/>
+      <c r="A101" s="78"/>
       <c r="B101" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C101" s="87"/>
+      <c r="C101" s="62"/>
       <c r="D101" s="6"/>
-      <c r="E101" s="87"/>
+      <c r="E101" s="62"/>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="7"/>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="74"/>
+      <c r="A102" s="78"/>
       <c r="B102" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C102" s="87"/>
+      <c r="C102" s="62"/>
       <c r="D102" s="6"/>
-      <c r="E102" s="87"/>
+      <c r="E102" s="62"/>
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
       <c r="H102" s="7"/>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="74"/>
+      <c r="A103" s="78"/>
       <c r="B103" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C103" s="88"/>
+      <c r="C103" s="63"/>
       <c r="D103" s="6"/>
-      <c r="E103" s="88"/>
+      <c r="E103" s="63"/>
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
       <c r="H103" s="7"/>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="74" t="s">
+      <c r="A104" s="78" t="s">
         <v>102</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="86"/>
+      <c r="C104" s="61"/>
       <c r="D104" s="6"/>
-      <c r="E104" s="86"/>
+      <c r="E104" s="61"/>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
       <c r="H104" s="7"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="74"/>
+      <c r="A105" s="78"/>
       <c r="B105" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C105" s="87"/>
+      <c r="C105" s="62"/>
       <c r="D105" s="6"/>
-      <c r="E105" s="87"/>
+      <c r="E105" s="62"/>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
       <c r="H105" s="7"/>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="74"/>
+      <c r="A106" s="78"/>
       <c r="B106" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="87"/>
+      <c r="C106" s="62"/>
       <c r="D106" s="6"/>
-      <c r="E106" s="87"/>
+      <c r="E106" s="62"/>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="7"/>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="74"/>
+      <c r="A107" s="78"/>
       <c r="B107" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C107" s="87"/>
+      <c r="C107" s="62"/>
       <c r="D107" s="6"/>
-      <c r="E107" s="87"/>
+      <c r="E107" s="62"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
       <c r="H107" s="7"/>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="74"/>
+      <c r="A108" s="78"/>
       <c r="B108" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="87"/>
+      <c r="C108" s="62"/>
       <c r="D108" s="6"/>
-      <c r="E108" s="87"/>
+      <c r="E108" s="62"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
       <c r="H108" s="7"/>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="74"/>
+      <c r="A109" s="78"/>
       <c r="B109" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C109" s="88"/>
+      <c r="C109" s="63"/>
       <c r="D109" s="6"/>
-      <c r="E109" s="88"/>
+      <c r="E109" s="63"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
       <c r="H109" s="7"/>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="74" t="s">
+      <c r="A110" s="78" t="s">
         <v>109</v>
       </c>
       <c r="B110" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C110" s="86"/>
+      <c r="C110" s="61"/>
       <c r="D110" s="6"/>
-      <c r="E110" s="86"/>
+      <c r="E110" s="61"/>
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
       <c r="H110" s="7"/>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="74"/>
+      <c r="A111" s="78"/>
       <c r="B111" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C111" s="87"/>
+      <c r="C111" s="62"/>
       <c r="D111" s="6"/>
-      <c r="E111" s="87"/>
+      <c r="E111" s="62"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="7"/>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="74"/>
+      <c r="A112" s="78"/>
       <c r="B112" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C112" s="87"/>
+      <c r="C112" s="62"/>
       <c r="D112" s="6"/>
-      <c r="E112" s="87"/>
+      <c r="E112" s="62"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
       <c r="H112" s="7"/>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="74"/>
+      <c r="A113" s="78"/>
       <c r="B113" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C113" s="87"/>
+      <c r="C113" s="62"/>
       <c r="D113" s="6"/>
-      <c r="E113" s="87"/>
+      <c r="E113" s="62"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
       <c r="H113" s="7"/>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="74"/>
+      <c r="A114" s="78"/>
       <c r="B114" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C114" s="88"/>
+      <c r="C114" s="63"/>
       <c r="D114" s="6"/>
-      <c r="E114" s="88"/>
+      <c r="E114" s="63"/>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="7"/>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="71" t="s">
+      <c r="A115" s="70" t="s">
         <v>115</v>
       </c>
       <c r="B115" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C115" s="86"/>
+      <c r="C115" s="61"/>
       <c r="D115" s="6"/>
-      <c r="E115" s="86"/>
+      <c r="E115" s="61"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="7"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="71"/>
+      <c r="A116" s="70"/>
       <c r="B116" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C116" s="87"/>
+      <c r="C116" s="62"/>
       <c r="D116" s="6"/>
-      <c r="E116" s="87"/>
+      <c r="E116" s="62"/>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
       <c r="H116" s="7"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="71"/>
+      <c r="A117" s="70"/>
       <c r="B117" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C117" s="87"/>
+      <c r="C117" s="62"/>
       <c r="D117" s="6"/>
-      <c r="E117" s="87"/>
+      <c r="E117" s="62"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="7"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="71"/>
+      <c r="A118" s="70"/>
       <c r="B118" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C118" s="87"/>
+      <c r="C118" s="62"/>
       <c r="D118" s="6"/>
-      <c r="E118" s="87"/>
+      <c r="E118" s="62"/>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="7"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="71"/>
+      <c r="A119" s="70"/>
       <c r="B119" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="87"/>
+      <c r="C119" s="62"/>
       <c r="D119" s="6"/>
-      <c r="E119" s="87"/>
+      <c r="E119" s="62"/>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
       <c r="H119" s="7"/>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="71"/>
+      <c r="A120" s="70"/>
       <c r="B120" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C120" s="87"/>
+      <c r="C120" s="62"/>
       <c r="D120" s="6"/>
-      <c r="E120" s="87"/>
+      <c r="E120" s="62"/>
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
       <c r="H120" s="7"/>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="71"/>
+      <c r="A121" s="70"/>
       <c r="B121" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="88"/>
+      <c r="C121" s="63"/>
       <c r="D121" s="6"/>
-      <c r="E121" s="88"/>
+      <c r="E121" s="63"/>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="7"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="71" t="s">
+      <c r="A122" s="70" t="s">
         <v>121</v>
       </c>
       <c r="B122" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C122" s="86"/>
+      <c r="C122" s="61"/>
       <c r="D122" s="6"/>
-      <c r="E122" s="86"/>
+      <c r="E122" s="61"/>
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
       <c r="H122" s="7"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="71"/>
+      <c r="A123" s="70"/>
       <c r="B123" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C123" s="87"/>
+      <c r="C123" s="62"/>
       <c r="D123" s="6"/>
-      <c r="E123" s="87"/>
+      <c r="E123" s="62"/>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
       <c r="H123" s="7"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="71"/>
+      <c r="A124" s="70"/>
       <c r="B124" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C124" s="87"/>
+      <c r="C124" s="62"/>
       <c r="D124" s="6"/>
-      <c r="E124" s="87"/>
+      <c r="E124" s="62"/>
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
       <c r="H124" s="7"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="71"/>
+      <c r="A125" s="70"/>
       <c r="B125" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C125" s="87"/>
+      <c r="C125" s="62"/>
       <c r="D125" s="6"/>
-      <c r="E125" s="87"/>
+      <c r="E125" s="62"/>
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
       <c r="H125" s="7"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="71"/>
+      <c r="A126" s="70"/>
       <c r="B126" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C126" s="87"/>
+      <c r="C126" s="62"/>
       <c r="D126" s="6"/>
-      <c r="E126" s="87"/>
+      <c r="E126" s="62"/>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
       <c r="H126" s="7"/>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="71"/>
+      <c r="A127" s="70"/>
       <c r="B127" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C127" s="87"/>
+      <c r="C127" s="62"/>
       <c r="D127" s="6"/>
-      <c r="E127" s="87"/>
+      <c r="E127" s="62"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
       <c r="H127" s="7"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="71"/>
+      <c r="A128" s="70"/>
       <c r="B128" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C128" s="87"/>
+      <c r="C128" s="62"/>
       <c r="D128" s="6"/>
-      <c r="E128" s="87"/>
+      <c r="E128" s="62"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
       <c r="H128" s="7"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="71"/>
+      <c r="A129" s="70"/>
       <c r="B129" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C129" s="88"/>
+      <c r="C129" s="63"/>
       <c r="D129" s="6"/>
-      <c r="E129" s="88"/>
+      <c r="E129" s="63"/>
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
       <c r="H129" s="7"/>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="34" t="s">
+      <c r="A130" s="33" t="s">
         <v>130</v>
       </c>
       <c r="B130" s="8" t="s">
@@ -3737,7 +3717,7 @@
       <c r="H130" s="7"/>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="34" t="s">
+      <c r="A131" s="33" t="s">
         <v>132</v>
       </c>
       <c r="B131" s="8" t="s">
@@ -3751,233 +3731,233 @@
       <c r="H131" s="7"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="77" t="s">
+      <c r="A132" s="71" t="s">
         <v>134</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C132" s="86">
+      <c r="C132" s="61">
         <v>3</v>
       </c>
       <c r="D132" s="6">
         <v>0</v>
       </c>
-      <c r="E132" s="86" t="s">
+      <c r="E132" s="61" t="s">
         <v>227</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G132" s="16"/>
-      <c r="H132" s="17"/>
+      <c r="G132" s="15"/>
+      <c r="H132" s="16"/>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="77"/>
+      <c r="A133" s="71"/>
       <c r="B133" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="C133" s="87"/>
+      <c r="C133" s="62"/>
       <c r="D133" s="6">
         <v>0</v>
       </c>
-      <c r="E133" s="87"/>
+      <c r="E133" s="62"/>
       <c r="F133" s="6" t="s">
         <v>226</v>
       </c>
       <c r="G133" s="6"/>
-      <c r="H133" s="17"/>
+      <c r="H133" s="16"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="77"/>
+      <c r="A134" s="71"/>
       <c r="B134" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C134" s="87"/>
+      <c r="C134" s="62"/>
       <c r="D134" s="6">
         <v>1</v>
       </c>
-      <c r="E134" s="87"/>
+      <c r="E134" s="62"/>
       <c r="F134" s="6" t="s">
         <v>227</v>
       </c>
       <c r="G134" s="6"/>
-      <c r="H134" s="17"/>
+      <c r="H134" s="16"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="77"/>
+      <c r="A135" s="71"/>
       <c r="B135" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C135" s="87"/>
+      <c r="C135" s="62"/>
       <c r="D135" s="6">
         <v>1</v>
       </c>
-      <c r="E135" s="87"/>
+      <c r="E135" s="62"/>
       <c r="F135" s="6" t="s">
         <v>227</v>
       </c>
       <c r="G135" s="6"/>
-      <c r="H135" s="17"/>
+      <c r="H135" s="16"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="77"/>
+      <c r="A136" s="71"/>
       <c r="B136" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C136" s="87"/>
+      <c r="C136" s="62"/>
       <c r="D136" s="6">
         <v>1</v>
       </c>
-      <c r="E136" s="87"/>
+      <c r="E136" s="62"/>
       <c r="F136" s="6" t="s">
         <v>227</v>
       </c>
       <c r="G136" s="6"/>
-      <c r="H136" s="30"/>
+      <c r="H136" s="29"/>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="77"/>
+      <c r="A137" s="71"/>
       <c r="B137" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C137" s="87"/>
+      <c r="C137" s="62"/>
       <c r="D137" s="6">
         <v>1</v>
       </c>
-      <c r="E137" s="87"/>
+      <c r="E137" s="62"/>
       <c r="F137" s="6" t="s">
         <v>227</v>
       </c>
       <c r="G137" s="6"/>
-      <c r="H137" s="17"/>
+      <c r="H137" s="16"/>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="77"/>
+      <c r="A138" s="71"/>
       <c r="B138" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C138" s="87"/>
+      <c r="C138" s="62"/>
       <c r="D138" s="6">
         <v>3</v>
       </c>
-      <c r="E138" s="87"/>
+      <c r="E138" s="62"/>
       <c r="F138" s="6" t="s">
         <v>227</v>
       </c>
       <c r="G138" s="6"/>
-      <c r="H138" s="17"/>
+      <c r="H138" s="16"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="77"/>
+      <c r="A139" s="71"/>
       <c r="B139" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C139" s="88"/>
+      <c r="C139" s="63"/>
       <c r="D139" s="6">
         <v>3</v>
       </c>
-      <c r="E139" s="88"/>
+      <c r="E139" s="63"/>
       <c r="F139" s="6" t="s">
         <v>227</v>
       </c>
       <c r="G139" s="6"/>
-      <c r="H139" s="17"/>
+      <c r="H139" s="16"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="78" t="s">
+      <c r="A140" s="72" t="s">
         <v>142</v>
       </c>
       <c r="B140" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C140" s="86"/>
+      <c r="C140" s="61"/>
       <c r="D140" s="6"/>
-      <c r="E140" s="86"/>
+      <c r="E140" s="61"/>
       <c r="F140" s="6"/>
       <c r="G140" s="6"/>
       <c r="H140" s="7"/>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="78"/>
+      <c r="A141" s="72"/>
       <c r="B141" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C141" s="87"/>
+      <c r="C141" s="62"/>
       <c r="D141" s="6"/>
-      <c r="E141" s="87"/>
+      <c r="E141" s="62"/>
       <c r="F141" s="6"/>
       <c r="G141" s="6"/>
       <c r="H141" s="7"/>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="78"/>
+      <c r="A142" s="72"/>
       <c r="B142" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C142" s="87"/>
+      <c r="C142" s="62"/>
       <c r="D142" s="6"/>
-      <c r="E142" s="87"/>
+      <c r="E142" s="62"/>
       <c r="F142" s="6"/>
       <c r="G142" s="6"/>
       <c r="H142" s="7"/>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="78"/>
+      <c r="A143" s="72"/>
       <c r="B143" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C143" s="87"/>
+      <c r="C143" s="62"/>
       <c r="D143" s="6"/>
-      <c r="E143" s="87"/>
+      <c r="E143" s="62"/>
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
       <c r="H143" s="7"/>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="78"/>
+      <c r="A144" s="72"/>
       <c r="B144" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C144" s="88"/>
+      <c r="C144" s="63"/>
       <c r="D144" s="6"/>
-      <c r="E144" s="88"/>
+      <c r="E144" s="63"/>
       <c r="F144" s="6"/>
       <c r="G144" s="6"/>
       <c r="H144" s="7"/>
     </row>
     <row r="145" spans="1:8">
-      <c r="A145" s="78" t="s">
+      <c r="A145" s="72" t="s">
         <v>148</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C145" s="86">
+      <c r="C145" s="61">
         <v>2</v>
       </c>
       <c r="D145" s="6">
         <v>0</v>
       </c>
-      <c r="E145" s="86" t="s">
+      <c r="E145" s="61" t="s">
         <v>227</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G145" s="16"/>
-      <c r="H145" s="17"/>
+      <c r="G145" s="15"/>
+      <c r="H145" s="16"/>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" s="78"/>
+      <c r="A146" s="72"/>
       <c r="B146" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C146" s="87"/>
+      <c r="C146" s="62"/>
       <c r="D146" s="6">
         <v>2</v>
       </c>
-      <c r="E146" s="87"/>
+      <c r="E146" s="62"/>
       <c r="F146" s="6" t="s">
         <v>227</v>
       </c>
@@ -3985,15 +3965,15 @@
       <c r="H146" s="7"/>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" s="78"/>
+      <c r="A147" s="72"/>
       <c r="B147" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C147" s="87"/>
+      <c r="C147" s="62"/>
       <c r="D147" s="6">
         <v>2</v>
       </c>
-      <c r="E147" s="87"/>
+      <c r="E147" s="62"/>
       <c r="F147" s="6" t="s">
         <v>227</v>
       </c>
@@ -4001,15 +3981,15 @@
       <c r="H147" s="7"/>
     </row>
     <row r="148" spans="1:8">
-      <c r="A148" s="78"/>
+      <c r="A148" s="72"/>
       <c r="B148" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="C148" s="87"/>
+      <c r="C148" s="62"/>
       <c r="D148" s="6">
         <v>2</v>
       </c>
-      <c r="E148" s="87"/>
+      <c r="E148" s="62"/>
       <c r="F148" s="6" t="s">
         <v>227</v>
       </c>
@@ -4017,15 +3997,15 @@
       <c r="H148" s="7"/>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="78"/>
+      <c r="A149" s="72"/>
       <c r="B149" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C149" s="87"/>
+      <c r="C149" s="62"/>
       <c r="D149" s="6">
         <v>2</v>
       </c>
-      <c r="E149" s="87"/>
+      <c r="E149" s="62"/>
       <c r="F149" s="6" t="s">
         <v>227</v>
       </c>
@@ -4033,15 +4013,15 @@
       <c r="H149" s="7"/>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="78"/>
+      <c r="A150" s="72"/>
       <c r="B150" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C150" s="87"/>
+      <c r="C150" s="62"/>
       <c r="D150" s="6">
         <v>2</v>
       </c>
-      <c r="E150" s="87"/>
+      <c r="E150" s="62"/>
       <c r="F150" s="6" t="s">
         <v>227</v>
       </c>
@@ -4049,15 +4029,15 @@
       <c r="H150" s="7"/>
     </row>
     <row r="151" spans="1:8">
-      <c r="A151" s="78"/>
+      <c r="A151" s="72"/>
       <c r="B151" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C151" s="88"/>
+      <c r="C151" s="63"/>
       <c r="D151" s="6">
         <v>2</v>
       </c>
-      <c r="E151" s="88"/>
+      <c r="E151" s="63"/>
       <c r="F151" s="6" t="s">
         <v>227</v>
       </c>
@@ -4065,245 +4045,245 @@
       <c r="H151" s="7"/>
     </row>
     <row r="152" spans="1:8" ht="18" customHeight="1">
-      <c r="A152" s="79" t="s">
+      <c r="A152" s="73" t="s">
         <v>155</v>
       </c>
       <c r="B152" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C152" s="86"/>
+      <c r="C152" s="61"/>
       <c r="D152" s="6"/>
-      <c r="E152" s="86"/>
+      <c r="E152" s="61"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
       <c r="H152" s="7"/>
     </row>
     <row r="153" spans="1:8">
-      <c r="A153" s="79"/>
+      <c r="A153" s="73"/>
       <c r="B153" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C153" s="87"/>
+      <c r="C153" s="62"/>
       <c r="D153" s="6"/>
-      <c r="E153" s="87"/>
+      <c r="E153" s="62"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
       <c r="H153" s="7"/>
     </row>
     <row r="154" spans="1:8">
-      <c r="A154" s="79"/>
+      <c r="A154" s="73"/>
       <c r="B154" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C154" s="87"/>
+      <c r="C154" s="62"/>
       <c r="D154" s="6"/>
-      <c r="E154" s="87"/>
+      <c r="E154" s="62"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
       <c r="H154" s="7"/>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" s="79"/>
+      <c r="A155" s="73"/>
       <c r="B155" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C155" s="87"/>
+      <c r="C155" s="62"/>
       <c r="D155" s="6"/>
-      <c r="E155" s="87"/>
+      <c r="E155" s="62"/>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
       <c r="H155" s="7"/>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" s="79"/>
+      <c r="A156" s="73"/>
       <c r="B156" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C156" s="87"/>
+      <c r="C156" s="62"/>
       <c r="D156" s="6"/>
-      <c r="E156" s="87"/>
+      <c r="E156" s="62"/>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
       <c r="H156" s="7"/>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" s="79"/>
+      <c r="A157" s="73"/>
       <c r="B157" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C157" s="88"/>
+      <c r="C157" s="63"/>
       <c r="D157" s="6"/>
-      <c r="E157" s="88"/>
+      <c r="E157" s="63"/>
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
       <c r="H157" s="7"/>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="79" t="s">
+      <c r="A158" s="73" t="s">
         <v>162</v>
       </c>
       <c r="B158" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C158" s="86"/>
+      <c r="C158" s="61"/>
       <c r="D158" s="6"/>
-      <c r="E158" s="86"/>
+      <c r="E158" s="61"/>
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
       <c r="H158" s="7"/>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" s="79"/>
+      <c r="A159" s="73"/>
       <c r="B159" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C159" s="87"/>
+      <c r="C159" s="62"/>
       <c r="D159" s="6"/>
-      <c r="E159" s="87"/>
+      <c r="E159" s="62"/>
       <c r="F159" s="6"/>
       <c r="G159" s="6"/>
       <c r="H159" s="7"/>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="79"/>
+      <c r="A160" s="73"/>
       <c r="B160" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C160" s="87"/>
+      <c r="C160" s="62"/>
       <c r="D160" s="6"/>
-      <c r="E160" s="87"/>
+      <c r="E160" s="62"/>
       <c r="F160" s="6"/>
       <c r="G160" s="6"/>
       <c r="H160" s="7"/>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="79"/>
+      <c r="A161" s="73"/>
       <c r="B161" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C161" s="88"/>
+      <c r="C161" s="63"/>
       <c r="D161" s="6"/>
-      <c r="E161" s="88"/>
+      <c r="E161" s="63"/>
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
       <c r="H161" s="7"/>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="80" t="s">
+      <c r="A162" s="74" t="s">
         <v>167</v>
       </c>
       <c r="B162" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C162" s="86">
+      <c r="C162" s="61">
         <v>1</v>
       </c>
       <c r="D162" s="6">
         <v>1</v>
       </c>
-      <c r="E162" s="86" t="s">
+      <c r="E162" s="61" t="s">
         <v>226</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G162" s="16"/>
-      <c r="H162" s="17"/>
+      <c r="G162" s="15"/>
+      <c r="H162" s="16"/>
     </row>
     <row r="163" spans="1:8">
-      <c r="A163" s="80"/>
+      <c r="A163" s="74"/>
       <c r="B163" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C163" s="87"/>
+      <c r="C163" s="62"/>
       <c r="D163" s="6">
         <v>0</v>
       </c>
-      <c r="E163" s="87"/>
+      <c r="E163" s="62"/>
       <c r="F163" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G163" s="16"/>
-      <c r="H163" s="17"/>
+      <c r="G163" s="15"/>
+      <c r="H163" s="16"/>
     </row>
     <row r="164" spans="1:8">
-      <c r="A164" s="80"/>
+      <c r="A164" s="74"/>
       <c r="B164" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C164" s="87"/>
+      <c r="C164" s="62"/>
       <c r="D164" s="6">
         <v>1</v>
       </c>
-      <c r="E164" s="87"/>
+      <c r="E164" s="62"/>
       <c r="F164" s="6" t="s">
         <v>224</v>
       </c>
       <c r="G164" s="6"/>
-      <c r="H164" s="17"/>
+      <c r="H164" s="16"/>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="80"/>
+      <c r="A165" s="74"/>
       <c r="B165" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C165" s="87"/>
+      <c r="C165" s="62"/>
       <c r="D165" s="6">
         <v>0</v>
       </c>
-      <c r="E165" s="87"/>
+      <c r="E165" s="62"/>
       <c r="F165" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G165" s="14"/>
-      <c r="H165" s="15"/>
+      <c r="G165" s="13"/>
+      <c r="H165" s="14"/>
     </row>
     <row r="166" spans="1:8">
-      <c r="A166" s="80"/>
+      <c r="A166" s="74"/>
       <c r="B166" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="C166" s="87"/>
+      <c r="C166" s="62"/>
       <c r="D166" s="6">
         <v>1</v>
       </c>
-      <c r="E166" s="87"/>
+      <c r="E166" s="62"/>
       <c r="F166" s="6" t="s">
         <v>226</v>
       </c>
       <c r="G166" s="6"/>
-      <c r="H166" s="30"/>
+      <c r="H166" s="29"/>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="80"/>
+      <c r="A167" s="74"/>
       <c r="B167" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C167" s="88"/>
+      <c r="C167" s="63"/>
       <c r="D167" s="6">
         <v>0</v>
       </c>
-      <c r="E167" s="88"/>
+      <c r="E167" s="63"/>
       <c r="F167" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G167" s="14"/>
-      <c r="H167" s="15"/>
+      <c r="G167" s="13"/>
+      <c r="H167" s="14"/>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="80" t="s">
+      <c r="A168" s="74" t="s">
         <v>171</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C168" s="86">
+      <c r="C168" s="61">
         <v>1</v>
       </c>
       <c r="D168" s="6">
         <v>1</v>
       </c>
-      <c r="E168" s="86" t="s">
+      <c r="E168" s="61" t="s">
         <v>226</v>
       </c>
       <c r="F168" s="6" t="s">
@@ -4313,19 +4293,19 @@
       <c r="H168" s="3"/>
     </row>
     <row r="169" spans="1:8">
-      <c r="A169" s="80"/>
+      <c r="A169" s="74"/>
       <c r="B169" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="C169" s="88"/>
+      <c r="C169" s="63"/>
       <c r="D169" s="6"/>
-      <c r="E169" s="88"/>
+      <c r="E169" s="63"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
       <c r="H169" s="7"/>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="35" t="s">
+      <c r="A170" s="34" t="s">
         <v>173</v>
       </c>
       <c r="B170" s="8" t="s">
@@ -4339,7 +4319,7 @@
       <c r="H170" s="7"/>
     </row>
     <row r="171" spans="1:8">
-      <c r="A171" s="35" t="s">
+      <c r="A171" s="34" t="s">
         <v>175</v>
       </c>
       <c r="B171" s="5" t="s">
@@ -4353,109 +4333,109 @@
       <c r="H171" s="7"/>
     </row>
     <row r="172" spans="1:8">
-      <c r="A172" s="81" t="s">
+      <c r="A172" s="75" t="s">
         <v>176</v>
       </c>
       <c r="B172" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C172" s="86">
+      <c r="C172" s="61">
         <v>2</v>
       </c>
       <c r="D172" s="6"/>
-      <c r="E172" s="86" t="s">
+      <c r="E172" s="61" t="s">
         <v>226</v>
       </c>
       <c r="F172" s="6"/>
-      <c r="G172" s="14"/>
-      <c r="H172" s="15"/>
+      <c r="G172" s="13"/>
+      <c r="H172" s="14"/>
     </row>
     <row r="173" spans="1:8">
-      <c r="A173" s="81"/>
+      <c r="A173" s="75"/>
       <c r="B173" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C173" s="87"/>
+      <c r="C173" s="62"/>
       <c r="D173" s="6"/>
-      <c r="E173" s="87"/>
+      <c r="E173" s="62"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
       <c r="H173" s="7"/>
     </row>
     <row r="174" spans="1:8">
-      <c r="A174" s="81"/>
+      <c r="A174" s="75"/>
       <c r="B174" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C174" s="87"/>
+      <c r="C174" s="62"/>
       <c r="D174" s="6"/>
-      <c r="E174" s="87"/>
+      <c r="E174" s="62"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
       <c r="H174" s="7"/>
     </row>
     <row r="175" spans="1:8">
-      <c r="A175" s="81"/>
+      <c r="A175" s="75"/>
       <c r="B175" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C175" s="87"/>
+      <c r="C175" s="62"/>
       <c r="D175" s="6"/>
-      <c r="E175" s="87"/>
+      <c r="E175" s="62"/>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
       <c r="H175" s="7"/>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" s="81"/>
+      <c r="A176" s="75"/>
       <c r="B176" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C176" s="87"/>
+      <c r="C176" s="62"/>
       <c r="D176" s="6"/>
-      <c r="E176" s="87"/>
+      <c r="E176" s="62"/>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
       <c r="H176" s="7"/>
     </row>
     <row r="177" spans="1:8">
-      <c r="A177" s="81"/>
+      <c r="A177" s="75"/>
       <c r="B177" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C177" s="87"/>
+      <c r="C177" s="62"/>
       <c r="D177" s="6"/>
-      <c r="E177" s="87"/>
+      <c r="E177" s="62"/>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
       <c r="H177" s="7"/>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="81"/>
+      <c r="A178" s="75"/>
       <c r="B178" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C178" s="87"/>
+      <c r="C178" s="62"/>
       <c r="D178" s="6"/>
-      <c r="E178" s="87"/>
+      <c r="E178" s="62"/>
       <c r="F178" s="6"/>
       <c r="G178" s="6"/>
       <c r="H178" s="7"/>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="81"/>
+      <c r="A179" s="75"/>
       <c r="B179" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C179" s="88"/>
+      <c r="C179" s="63"/>
       <c r="D179" s="6"/>
-      <c r="E179" s="88"/>
+      <c r="E179" s="63"/>
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
       <c r="H179" s="7"/>
     </row>
     <row r="180" spans="1:8">
-      <c r="A180" s="36" t="s">
+      <c r="A180" s="35" t="s">
         <v>184</v>
       </c>
       <c r="B180" s="5" t="s">
@@ -4465,11 +4445,11 @@
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
       <c r="F180" s="6"/>
-      <c r="G180" s="12"/>
-      <c r="H180" s="13"/>
+      <c r="G180" s="11"/>
+      <c r="H180" s="12"/>
     </row>
     <row r="181" spans="1:8">
-      <c r="A181" s="36" t="s">
+      <c r="A181" s="35" t="s">
         <v>186</v>
       </c>
       <c r="B181" s="8" t="s">
@@ -4479,11 +4459,11 @@
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
-      <c r="G181" s="12"/>
-      <c r="H181" s="13"/>
+      <c r="G181" s="11"/>
+      <c r="H181" s="12"/>
     </row>
     <row r="182" spans="1:8">
-      <c r="A182" s="36" t="s">
+      <c r="A182" s="35" t="s">
         <v>188</v>
       </c>
       <c r="B182" s="8" t="s">
@@ -4493,11 +4473,11 @@
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
       <c r="F182" s="6"/>
-      <c r="G182" s="12"/>
-      <c r="H182" s="13"/>
+      <c r="G182" s="11"/>
+      <c r="H182" s="12"/>
     </row>
     <row r="183" spans="1:8">
-      <c r="A183" s="36" t="s">
+      <c r="A183" s="35" t="s">
         <v>190</v>
       </c>
       <c r="B183" s="5" t="s">
@@ -4507,11 +4487,11 @@
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
-      <c r="G183" s="12"/>
-      <c r="H183" s="13"/>
+      <c r="G183" s="11"/>
+      <c r="H183" s="12"/>
     </row>
     <row r="184" spans="1:8">
-      <c r="A184" s="36" t="s">
+      <c r="A184" s="35" t="s">
         <v>192</v>
       </c>
       <c r="B184" s="8" t="s">
@@ -4521,456 +4501,504 @@
       <c r="D184" s="6"/>
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
-      <c r="G184" s="12"/>
-      <c r="H184" s="13"/>
+      <c r="G184" s="11"/>
+      <c r="H184" s="12"/>
     </row>
     <row r="185" spans="1:8">
-      <c r="A185" s="75" t="s">
+      <c r="A185" s="68" t="s">
         <v>193</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C185" s="86"/>
+      <c r="C185" s="61"/>
       <c r="D185" s="6"/>
-      <c r="E185" s="86"/>
+      <c r="E185" s="61"/>
       <c r="F185" s="6"/>
-      <c r="G185" s="12"/>
-      <c r="H185" s="13"/>
+      <c r="G185" s="11"/>
+      <c r="H185" s="12"/>
     </row>
     <row r="186" spans="1:8">
-      <c r="A186" s="75"/>
+      <c r="A186" s="68"/>
       <c r="B186" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C186" s="87"/>
+      <c r="C186" s="62"/>
       <c r="D186" s="6"/>
-      <c r="E186" s="87"/>
+      <c r="E186" s="62"/>
       <c r="F186" s="6"/>
-      <c r="G186" s="12"/>
-      <c r="H186" s="13"/>
+      <c r="G186" s="11"/>
+      <c r="H186" s="12"/>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="75"/>
+      <c r="A187" s="68"/>
       <c r="B187" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C187" s="87"/>
+      <c r="C187" s="62"/>
       <c r="D187" s="6"/>
-      <c r="E187" s="87"/>
+      <c r="E187" s="62"/>
       <c r="F187" s="6"/>
-      <c r="G187" s="12"/>
-      <c r="H187" s="13"/>
+      <c r="G187" s="11"/>
+      <c r="H187" s="12"/>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="75"/>
+      <c r="A188" s="68"/>
       <c r="B188" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C188" s="87"/>
+      <c r="C188" s="62"/>
       <c r="D188" s="6"/>
-      <c r="E188" s="87"/>
+      <c r="E188" s="62"/>
       <c r="F188" s="6"/>
-      <c r="G188" s="12"/>
-      <c r="H188" s="13"/>
+      <c r="G188" s="11"/>
+      <c r="H188" s="12"/>
     </row>
     <row r="189" spans="1:8">
-      <c r="A189" s="75"/>
+      <c r="A189" s="68"/>
       <c r="B189" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C189" s="87"/>
+      <c r="C189" s="62"/>
       <c r="D189" s="6"/>
-      <c r="E189" s="87"/>
+      <c r="E189" s="62"/>
       <c r="F189" s="6"/>
-      <c r="G189" s="12"/>
-      <c r="H189" s="13"/>
+      <c r="G189" s="11"/>
+      <c r="H189" s="12"/>
     </row>
     <row r="190" spans="1:8">
-      <c r="A190" s="75"/>
+      <c r="A190" s="68"/>
       <c r="B190" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C190" s="88"/>
+      <c r="C190" s="63"/>
       <c r="D190" s="6"/>
-      <c r="E190" s="88"/>
+      <c r="E190" s="63"/>
       <c r="F190" s="6"/>
-      <c r="G190" s="12"/>
-      <c r="H190" s="13"/>
+      <c r="G190" s="11"/>
+      <c r="H190" s="12"/>
     </row>
     <row r="191" spans="1:8">
-      <c r="A191" s="75" t="s">
+      <c r="A191" s="68" t="s">
         <v>200</v>
       </c>
       <c r="B191" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C191" s="86"/>
+      <c r="C191" s="61"/>
       <c r="D191" s="6"/>
-      <c r="E191" s="86"/>
+      <c r="E191" s="61"/>
       <c r="F191" s="6"/>
-      <c r="G191" s="12"/>
-      <c r="H191" s="13"/>
+      <c r="G191" s="11"/>
+      <c r="H191" s="12"/>
     </row>
     <row r="192" spans="1:8">
-      <c r="A192" s="75"/>
+      <c r="A192" s="68"/>
       <c r="B192" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C192" s="87"/>
+      <c r="C192" s="62"/>
       <c r="D192" s="6"/>
-      <c r="E192" s="87"/>
+      <c r="E192" s="62"/>
       <c r="F192" s="6"/>
-      <c r="G192" s="12"/>
-      <c r="H192" s="13"/>
+      <c r="G192" s="11"/>
+      <c r="H192" s="12"/>
     </row>
     <row r="193" spans="1:8">
-      <c r="A193" s="75"/>
+      <c r="A193" s="68"/>
       <c r="B193" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C193" s="87"/>
+      <c r="C193" s="62"/>
       <c r="D193" s="6"/>
-      <c r="E193" s="87"/>
+      <c r="E193" s="62"/>
       <c r="F193" s="6"/>
-      <c r="G193" s="12"/>
-      <c r="H193" s="13"/>
+      <c r="G193" s="11"/>
+      <c r="H193" s="12"/>
     </row>
     <row r="194" spans="1:8">
-      <c r="A194" s="75"/>
+      <c r="A194" s="68"/>
       <c r="B194" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C194" s="87"/>
+      <c r="C194" s="62"/>
       <c r="D194" s="6"/>
-      <c r="E194" s="87"/>
+      <c r="E194" s="62"/>
       <c r="F194" s="6"/>
-      <c r="G194" s="12"/>
-      <c r="H194" s="13"/>
+      <c r="G194" s="11"/>
+      <c r="H194" s="12"/>
     </row>
     <row r="195" spans="1:8">
-      <c r="A195" s="75"/>
+      <c r="A195" s="68"/>
       <c r="B195" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="C195" s="87"/>
+      <c r="C195" s="62"/>
       <c r="D195" s="6"/>
-      <c r="E195" s="87"/>
+      <c r="E195" s="62"/>
       <c r="F195" s="6"/>
-      <c r="G195" s="12"/>
-      <c r="H195" s="13"/>
+      <c r="G195" s="11"/>
+      <c r="H195" s="12"/>
     </row>
     <row r="196" spans="1:8">
-      <c r="A196" s="75"/>
+      <c r="A196" s="68"/>
       <c r="B196" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C196" s="87"/>
+      <c r="C196" s="62"/>
       <c r="D196" s="6"/>
-      <c r="E196" s="87"/>
+      <c r="E196" s="62"/>
       <c r="F196" s="6"/>
-      <c r="G196" s="12"/>
-      <c r="H196" s="13"/>
+      <c r="G196" s="11"/>
+      <c r="H196" s="12"/>
     </row>
     <row r="197" spans="1:8">
-      <c r="A197" s="75"/>
+      <c r="A197" s="68"/>
       <c r="B197" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C197" s="87"/>
+      <c r="C197" s="62"/>
       <c r="D197" s="6"/>
-      <c r="E197" s="87"/>
+      <c r="E197" s="62"/>
       <c r="F197" s="6"/>
-      <c r="G197" s="12"/>
-      <c r="H197" s="13"/>
+      <c r="G197" s="11"/>
+      <c r="H197" s="12"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="75"/>
+      <c r="A198" s="68"/>
       <c r="B198" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C198" s="87"/>
+      <c r="C198" s="62"/>
       <c r="D198" s="6"/>
-      <c r="E198" s="87"/>
+      <c r="E198" s="62"/>
       <c r="F198" s="6"/>
-      <c r="G198" s="12"/>
-      <c r="H198" s="13"/>
+      <c r="G198" s="11"/>
+      <c r="H198" s="12"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="75"/>
+      <c r="A199" s="68"/>
       <c r="B199" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C199" s="88"/>
+      <c r="C199" s="63"/>
       <c r="D199" s="6"/>
-      <c r="E199" s="88"/>
+      <c r="E199" s="63"/>
       <c r="F199" s="6"/>
-      <c r="G199" s="12"/>
-      <c r="H199" s="13"/>
+      <c r="G199" s="11"/>
+      <c r="H199" s="12"/>
     </row>
     <row r="200" spans="1:8">
-      <c r="A200" s="75" t="s">
+      <c r="A200" s="68" t="s">
         <v>210</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C200" s="86"/>
+      <c r="C200" s="61"/>
       <c r="D200" s="6"/>
-      <c r="E200" s="86"/>
+      <c r="E200" s="61"/>
       <c r="F200" s="6"/>
-      <c r="G200" s="12"/>
-      <c r="H200" s="13"/>
+      <c r="G200" s="11"/>
+      <c r="H200" s="12"/>
     </row>
     <row r="201" spans="1:8">
-      <c r="A201" s="75"/>
+      <c r="A201" s="68"/>
       <c r="B201" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="C201" s="87"/>
+      <c r="C201" s="62"/>
       <c r="D201" s="6"/>
-      <c r="E201" s="87"/>
+      <c r="E201" s="62"/>
       <c r="F201" s="6"/>
-      <c r="G201" s="12"/>
-      <c r="H201" s="13"/>
+      <c r="G201" s="11"/>
+      <c r="H201" s="12"/>
     </row>
     <row r="202" spans="1:8">
-      <c r="A202" s="75"/>
+      <c r="A202" s="68"/>
       <c r="B202" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C202" s="87"/>
+      <c r="C202" s="62"/>
       <c r="D202" s="6"/>
-      <c r="E202" s="87"/>
+      <c r="E202" s="62"/>
       <c r="F202" s="6"/>
-      <c r="G202" s="12"/>
-      <c r="H202" s="13"/>
+      <c r="G202" s="11"/>
+      <c r="H202" s="12"/>
     </row>
     <row r="203" spans="1:8">
-      <c r="A203" s="75"/>
+      <c r="A203" s="68"/>
       <c r="B203" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="C203" s="87"/>
+      <c r="C203" s="62"/>
       <c r="D203" s="6"/>
-      <c r="E203" s="87"/>
+      <c r="E203" s="62"/>
       <c r="F203" s="6"/>
-      <c r="G203" s="12"/>
-      <c r="H203" s="13"/>
+      <c r="G203" s="11"/>
+      <c r="H203" s="12"/>
     </row>
     <row r="204" spans="1:8">
-      <c r="A204" s="75"/>
+      <c r="A204" s="68"/>
       <c r="B204" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C204" s="87"/>
+      <c r="C204" s="62"/>
       <c r="D204" s="6"/>
-      <c r="E204" s="87"/>
+      <c r="E204" s="62"/>
       <c r="F204" s="6"/>
-      <c r="G204" s="12"/>
-      <c r="H204" s="13"/>
+      <c r="G204" s="11"/>
+      <c r="H204" s="12"/>
     </row>
     <row r="205" spans="1:8">
-      <c r="A205" s="75"/>
+      <c r="A205" s="68"/>
       <c r="B205" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="C205" s="87"/>
+      <c r="C205" s="62"/>
       <c r="D205" s="6"/>
-      <c r="E205" s="87"/>
+      <c r="E205" s="62"/>
       <c r="F205" s="6"/>
-      <c r="G205" s="12"/>
-      <c r="H205" s="13"/>
+      <c r="G205" s="11"/>
+      <c r="H205" s="12"/>
     </row>
     <row r="206" spans="1:8">
-      <c r="A206" s="75"/>
+      <c r="A206" s="68"/>
       <c r="B206" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C206" s="87"/>
+      <c r="C206" s="62"/>
       <c r="D206" s="6"/>
-      <c r="E206" s="87"/>
+      <c r="E206" s="62"/>
       <c r="F206" s="6"/>
-      <c r="G206" s="12"/>
-      <c r="H206" s="13"/>
+      <c r="G206" s="11"/>
+      <c r="H206" s="12"/>
     </row>
     <row r="207" spans="1:8">
-      <c r="A207" s="75"/>
+      <c r="A207" s="68"/>
       <c r="B207" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="C207" s="87"/>
+      <c r="C207" s="62"/>
       <c r="D207" s="6"/>
-      <c r="E207" s="87"/>
+      <c r="E207" s="62"/>
       <c r="F207" s="6"/>
-      <c r="G207" s="12"/>
-      <c r="H207" s="13"/>
+      <c r="G207" s="11"/>
+      <c r="H207" s="12"/>
     </row>
     <row r="208" spans="1:8">
-      <c r="A208" s="75"/>
+      <c r="A208" s="68"/>
       <c r="B208" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C208" s="87"/>
+      <c r="C208" s="62"/>
       <c r="D208" s="6"/>
-      <c r="E208" s="87"/>
+      <c r="E208" s="62"/>
       <c r="F208" s="6"/>
-      <c r="G208" s="12"/>
-      <c r="H208" s="13"/>
+      <c r="G208" s="11"/>
+      <c r="H208" s="12"/>
     </row>
     <row r="209" spans="1:8">
-      <c r="A209" s="75"/>
+      <c r="A209" s="68"/>
       <c r="B209" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C209" s="87"/>
+      <c r="C209" s="62"/>
       <c r="D209" s="6"/>
-      <c r="E209" s="87"/>
+      <c r="E209" s="62"/>
       <c r="F209" s="6"/>
-      <c r="G209" s="12"/>
-      <c r="H209" s="13"/>
+      <c r="G209" s="11"/>
+      <c r="H209" s="12"/>
     </row>
     <row r="210" spans="1:8">
-      <c r="A210" s="76"/>
-      <c r="B210" s="19" t="s">
+      <c r="A210" s="69"/>
+      <c r="B210" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="C210" s="87"/>
-      <c r="D210" s="18"/>
-      <c r="E210" s="87"/>
-      <c r="F210" s="18"/>
-      <c r="G210" s="20"/>
-      <c r="H210" s="21"/>
+      <c r="C210" s="62"/>
+      <c r="D210" s="17"/>
+      <c r="E210" s="62"/>
+      <c r="F210" s="17"/>
+      <c r="G210" s="19"/>
+      <c r="H210" s="20"/>
     </row>
     <row r="211" spans="1:8">
-      <c r="A211" s="33" t="s">
+      <c r="A211" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="B211" s="22" t="s">
+      <c r="B211" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="C211" s="23">
+      <c r="C211" s="22">
         <v>4</v>
       </c>
-      <c r="D211" s="23">
+      <c r="D211" s="22">
         <v>4</v>
       </c>
-      <c r="E211" s="23" t="s">
+      <c r="E211" s="22" t="s">
         <v>253</v>
       </c>
-      <c r="F211" s="23" t="s">
+      <c r="F211" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="G211" s="24"/>
-      <c r="H211" s="24"/>
+      <c r="G211" s="23"/>
+      <c r="H211" s="23"/>
     </row>
     <row r="212" spans="1:8">
-      <c r="A212" s="62" t="s">
+      <c r="A212" s="81" t="s">
         <v>231</v>
       </c>
-      <c r="B212" s="22" t="s">
+      <c r="B212" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="C212" s="64">
+      <c r="C212" s="83">
         <v>3</v>
       </c>
-      <c r="D212" s="46">
+      <c r="D212" s="45">
         <v>3</v>
       </c>
-      <c r="E212" s="64" t="s">
+      <c r="E212" s="83" t="s">
         <v>253</v>
       </c>
-      <c r="F212" s="46" t="s">
+      <c r="F212" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="G212" s="46"/>
-      <c r="H212" s="53"/>
+      <c r="G212" s="45"/>
+      <c r="H212" s="52"/>
     </row>
     <row r="213" spans="1:8">
-      <c r="A213" s="63"/>
-      <c r="B213" s="22" t="s">
+      <c r="A213" s="82"/>
+      <c r="B213" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="C213" s="65"/>
-      <c r="D213" s="23"/>
-      <c r="E213" s="65"/>
-      <c r="F213" s="23"/>
-      <c r="G213" s="23"/>
-      <c r="H213" s="22"/>
+      <c r="C213" s="84"/>
+      <c r="D213" s="22"/>
+      <c r="E213" s="84"/>
+      <c r="F213" s="22"/>
+      <c r="G213" s="22"/>
+      <c r="H213" s="21"/>
     </row>
     <row r="214" spans="1:8">
-      <c r="A214" s="66" t="s">
+      <c r="A214" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="B214" s="22" t="s">
+      <c r="B214" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="C214" s="67"/>
-      <c r="D214" s="23"/>
-      <c r="E214" s="67"/>
-      <c r="F214" s="23"/>
-      <c r="G214" s="24"/>
-      <c r="H214" s="24"/>
+      <c r="C214" s="86"/>
+      <c r="D214" s="22"/>
+      <c r="E214" s="86"/>
+      <c r="F214" s="22"/>
+      <c r="G214" s="23"/>
+      <c r="H214" s="23"/>
     </row>
     <row r="215" spans="1:8">
-      <c r="A215" s="66"/>
-      <c r="B215" s="50" t="s">
+      <c r="A215" s="85"/>
+      <c r="B215" s="49" t="s">
         <v>235</v>
       </c>
-      <c r="C215" s="68"/>
-      <c r="D215" s="51"/>
-      <c r="E215" s="68"/>
-      <c r="F215" s="51"/>
-      <c r="G215" s="52"/>
-      <c r="H215" s="52"/>
+      <c r="C215" s="87"/>
+      <c r="D215" s="50"/>
+      <c r="E215" s="87"/>
+      <c r="F215" s="50"/>
+      <c r="G215" s="51"/>
+      <c r="H215" s="51"/>
     </row>
     <row r="216" spans="1:8">
-      <c r="A216" s="49" t="s">
+      <c r="A216" s="48" t="s">
         <v>255</v>
       </c>
-      <c r="B216" s="54" t="s">
+      <c r="B216" s="53" t="s">
         <v>256</v>
       </c>
-      <c r="C216" s="48"/>
-      <c r="D216" s="48"/>
-      <c r="E216" s="48"/>
-      <c r="F216" s="48"/>
-      <c r="G216" s="55"/>
-      <c r="H216" s="55"/>
+      <c r="C216" s="47"/>
+      <c r="D216" s="47"/>
+      <c r="E216" s="47"/>
+      <c r="F216" s="47"/>
+      <c r="G216" s="54"/>
+      <c r="H216" s="54"/>
     </row>
     <row r="217" spans="1:8">
-      <c r="A217" s="56" t="s">
+      <c r="A217" s="55" t="s">
         <v>258</v>
       </c>
-      <c r="B217" s="57" t="s">
+      <c r="B217" s="56" t="s">
         <v>259</v>
       </c>
-      <c r="C217" s="47"/>
-      <c r="D217" s="47"/>
-      <c r="E217" s="47"/>
-      <c r="F217" s="47"/>
-      <c r="G217" s="47"/>
-      <c r="H217" s="47"/>
+      <c r="C217" s="46"/>
+      <c r="D217" s="46"/>
+      <c r="E217" s="46"/>
+      <c r="F217" s="46"/>
+      <c r="G217" s="46"/>
+      <c r="H217" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="C185:C190"/>
-    <mergeCell ref="E185:E190"/>
-    <mergeCell ref="C191:C199"/>
-    <mergeCell ref="E191:E199"/>
-    <mergeCell ref="C200:C210"/>
-    <mergeCell ref="E200:E210"/>
-    <mergeCell ref="C162:C167"/>
-    <mergeCell ref="E162:E167"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="E168:E169"/>
-    <mergeCell ref="C172:C179"/>
-    <mergeCell ref="E172:E179"/>
-    <mergeCell ref="C152:C157"/>
-    <mergeCell ref="E145:E151"/>
-    <mergeCell ref="E152:E157"/>
-    <mergeCell ref="C158:C161"/>
-    <mergeCell ref="E158:E161"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="E212:E213"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="E214:E215"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A9:A16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="A26:A33"/>
+    <mergeCell ref="A115:A121"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="A48:A52"/>
+    <mergeCell ref="A53:A60"/>
+    <mergeCell ref="A61:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A80"/>
+    <mergeCell ref="A81:A89"/>
+    <mergeCell ref="A90:A98"/>
+    <mergeCell ref="A99:A103"/>
+    <mergeCell ref="A104:A109"/>
+    <mergeCell ref="A110:A114"/>
+    <mergeCell ref="A200:A210"/>
+    <mergeCell ref="A122:A129"/>
+    <mergeCell ref="A132:A139"/>
+    <mergeCell ref="A140:A144"/>
+    <mergeCell ref="A145:A151"/>
+    <mergeCell ref="A152:A157"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="A162:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A172:A179"/>
+    <mergeCell ref="A185:A190"/>
+    <mergeCell ref="A191:A199"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C2:C8"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E2:E8"/>
+    <mergeCell ref="C9:C16"/>
+    <mergeCell ref="E9:E16"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="E17:E20"/>
+    <mergeCell ref="C21:C25"/>
+    <mergeCell ref="E21:E25"/>
+    <mergeCell ref="C26:C33"/>
+    <mergeCell ref="E26:E33"/>
+    <mergeCell ref="C34:C40"/>
+    <mergeCell ref="E34:E40"/>
+    <mergeCell ref="C41:C47"/>
+    <mergeCell ref="E41:E47"/>
+    <mergeCell ref="C48:C52"/>
+    <mergeCell ref="E48:E52"/>
+    <mergeCell ref="C53:C60"/>
+    <mergeCell ref="E53:E60"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="E61:E66"/>
+    <mergeCell ref="C61:C66"/>
+    <mergeCell ref="C132:C139"/>
+    <mergeCell ref="E132:E139"/>
+    <mergeCell ref="C140:C144"/>
+    <mergeCell ref="E140:E144"/>
+    <mergeCell ref="C122:C129"/>
     <mergeCell ref="C81:C89"/>
     <mergeCell ref="E81:E89"/>
     <mergeCell ref="C69:C80"/>
@@ -4987,71 +5015,23 @@
     <mergeCell ref="C110:C114"/>
     <mergeCell ref="E110:E114"/>
     <mergeCell ref="E122:E129"/>
-    <mergeCell ref="C132:C139"/>
-    <mergeCell ref="E132:E139"/>
-    <mergeCell ref="C140:C144"/>
-    <mergeCell ref="E140:E144"/>
-    <mergeCell ref="C122:C129"/>
-    <mergeCell ref="C53:C60"/>
-    <mergeCell ref="E53:E60"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="E61:E66"/>
-    <mergeCell ref="C61:C66"/>
-    <mergeCell ref="C34:C40"/>
-    <mergeCell ref="E34:E40"/>
-    <mergeCell ref="C41:C47"/>
-    <mergeCell ref="E41:E47"/>
-    <mergeCell ref="C48:C52"/>
-    <mergeCell ref="E48:E52"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="C21:C25"/>
-    <mergeCell ref="E21:E25"/>
-    <mergeCell ref="C26:C33"/>
-    <mergeCell ref="E26:E33"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C2:C8"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="E2:E8"/>
-    <mergeCell ref="C9:C16"/>
-    <mergeCell ref="E9:E16"/>
-    <mergeCell ref="A200:A210"/>
-    <mergeCell ref="A122:A129"/>
-    <mergeCell ref="A132:A139"/>
-    <mergeCell ref="A140:A144"/>
-    <mergeCell ref="A145:A151"/>
-    <mergeCell ref="A152:A157"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="A162:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A172:A179"/>
-    <mergeCell ref="A185:A190"/>
-    <mergeCell ref="A191:A199"/>
-    <mergeCell ref="A115:A121"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="A48:A52"/>
-    <mergeCell ref="A53:A60"/>
-    <mergeCell ref="A61:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A80"/>
-    <mergeCell ref="A81:A89"/>
-    <mergeCell ref="A90:A98"/>
-    <mergeCell ref="A99:A103"/>
-    <mergeCell ref="A104:A109"/>
-    <mergeCell ref="A110:A114"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="A2:A8"/>
-    <mergeCell ref="A9:A16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="E212:E213"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="E214:E215"/>
+    <mergeCell ref="C152:C157"/>
+    <mergeCell ref="E145:E151"/>
+    <mergeCell ref="E152:E157"/>
+    <mergeCell ref="C158:C161"/>
+    <mergeCell ref="E158:E161"/>
+    <mergeCell ref="C162:C167"/>
+    <mergeCell ref="E162:E167"/>
+    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="E168:E169"/>
+    <mergeCell ref="C172:C179"/>
+    <mergeCell ref="E172:E179"/>
+    <mergeCell ref="C185:C190"/>
+    <mergeCell ref="E185:E190"/>
+    <mergeCell ref="C191:C199"/>
+    <mergeCell ref="E191:E199"/>
+    <mergeCell ref="C200:C210"/>
+    <mergeCell ref="E200:E210"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
